--- a/products.xlsx
+++ b/products.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="76">
   <si>
     <t>ID</t>
   </si>
@@ -143,6 +143,9 @@
     <t>LIGHTGREY</t>
   </si>
   <si>
+    <t>Ladies, Jacket, Outerwear, Knitwear</t>
+  </si>
+  <si>
     <t>MS14-1072</t>
   </si>
   <si>
@@ -155,6 +158,9 @@
     <t>LADIES100COTTONSINGEDJERSEYDIPDYEDVEST</t>
   </si>
   <si>
+    <t>Ladies, Vest, Outerwear, Knitwear</t>
+  </si>
+  <si>
     <t>POWDEREDROSE</t>
   </si>
   <si>
@@ -173,6 +179,9 @@
     <t>LADIES100COTTONSINGEDJERSEYDIPDYEDPANTS</t>
   </si>
   <si>
+    <t>Ladies, Pants, Bottoms, Knitwear</t>
+  </si>
+  <si>
     <t>LADIES100COTTONSINGEDJERSEYDPANTS</t>
   </si>
   <si>
@@ -188,18 +197,27 @@
     <t>LADIESTANKTOP</t>
   </si>
   <si>
+    <t>Ladies, Top, Knitwear</t>
+  </si>
+  <si>
     <t>MS141070</t>
   </si>
   <si>
     <t>100COTTONSINGEDJERSEYDIPDYEDBEANIE</t>
   </si>
   <si>
+    <t>Unisex, Beanie, Headwear, Knitwear</t>
+  </si>
+  <si>
     <t>AS151003</t>
   </si>
   <si>
     <t>100COTTONSINGEDJERSEYDIPDYEDSCARF</t>
   </si>
   <si>
+    <t>Unisex, Scarf, Accessories, Knitwear</t>
+  </si>
+  <si>
     <t>MS14-1066</t>
   </si>
   <si>
@@ -213,6 +231,9 @@
   </si>
   <si>
     <t>LADIES100COTTONSINGEDJERSEYDIPDYEDTEE</t>
+  </si>
+  <si>
+    <t>Ladies, Top, Knitwear, Tee</t>
   </si>
   <si>
     <t>LADIESCREWNECK(METALIC)100COTTONSINGEDJERSEYDIPDYEDTEE</t>
@@ -246,7 +267,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -265,6 +286,12 @@
       <sz val="10.95"/>
       <color rgb="FF000000"/>
       <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0F1115"/>
+      <name val="Helvetica Neue"/>
       <charset val="134"/>
     </font>
     <font>
@@ -729,162 +756,174 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1363,3848 +1402,3937 @@
   <dimension ref="A1:O1000"/>
   <sheetFormatPr defaultColWidth="12.6339285714286" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.25" customWidth="1"/>
-    <col min="2" max="2" width="47.1785714285714" customWidth="1"/>
-    <col min="4" max="4" width="11.0714285714286" customWidth="1"/>
-    <col min="5" max="5" width="52.7857142857143" customWidth="1"/>
-    <col min="6" max="6" width="26.5446428571429" customWidth="1"/>
+    <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.3303571428571" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6339285714286" style="1"/>
+    <col min="4" max="4" width="11.0714285714286" style="1" customWidth="1"/>
+    <col min="5" max="5" width="60.6696428571429" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5446428571429" style="1" customWidth="1"/>
+    <col min="7" max="12" width="5.58035714285714" style="1" customWidth="1"/>
+    <col min="13" max="13" width="6.58035714285714" style="1" customWidth="1"/>
+    <col min="14" max="14" width="34.1964285714286" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="12.6339285714286" style="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:15">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:15">
-      <c r="A2">
+      <c r="A2" s="1">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="3">
         <v>1</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <v>188</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" ht="16" spans="1:15">
-      <c r="A3">
+    <row r="3" ht="29" spans="1:15">
+      <c r="A3" s="1">
         <v>9</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="3">
         <v>1</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>189</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:15">
-      <c r="A4">
+      <c r="A4" s="1">
         <v>10</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="3">
         <v>3</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>190</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:15">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>11</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="3">
         <v>1</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>191</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:15">
-      <c r="A6">
+      <c r="A6" s="1">
         <v>12</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="3">
         <v>1</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>192</v>
       </c>
-      <c r="N6" t="s">
+      <c r="N6" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:15">
-      <c r="A7">
+      <c r="A7" s="1">
         <v>13</v>
       </c>
-      <c r="B7" s="3" t="str">
+      <c r="B7" s="4" t="str">
         <f t="shared" ref="B7:B13" si="0">A7&amp;D7&amp;"_"&amp;F7</f>
         <v>13AS151000_GREYMELANGE+OLDROSE</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="3">
         <v>1</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>193</v>
       </c>
-      <c r="N7" t="s">
+      <c r="N7" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:15">
-      <c r="A8">
+      <c r="A8" s="1">
         <v>14</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="3">
         <v>2</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>194</v>
       </c>
-      <c r="N8" t="s">
-        <v>20</v>
+      <c r="N8" s="6" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:15">
-      <c r="A9">
+      <c r="A9" s="1">
         <v>15</v>
       </c>
-      <c r="B9" s="3" t="str">
+      <c r="B9" s="4" t="str">
         <f t="shared" si="0"/>
         <v>15MS14-1072_SORBET</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="1">
+        <v>2</v>
+      </c>
+      <c r="M9" s="1">
+        <v>195</v>
+      </c>
+      <c r="N9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9">
-        <v>2</v>
-      </c>
-      <c r="M9">
-        <v>195</v>
-      </c>
     </row>
     <row r="10" customHeight="1" spans="1:15">
-      <c r="A10">
+      <c r="A10" s="1">
         <v>16</v>
       </c>
-      <c r="B10" s="3" t="str">
+      <c r="B10" s="4" t="str">
         <f>D10&amp;"_"&amp;F10&amp;".png"</f>
         <v>MS14-1071_PINE.png</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="D10" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="F10" t="s">
+      <c r="E10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>1</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>196</v>
       </c>
+      <c r="N10" s="6" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="11" customHeight="1" spans="1:15">
-      <c r="A11">
+      <c r="A11" s="1">
         <v>17</v>
       </c>
-      <c r="B11" s="3" t="str">
+      <c r="B11" s="4" t="str">
         <f t="shared" si="0"/>
         <v>17MS14-1071_LIGHTGREY</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="D11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="F11" t="s">
+      <c r="E11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>2</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>197</v>
       </c>
+      <c r="N11" s="6" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="12" customHeight="1" spans="1:15">
-      <c r="A12">
+      <c r="A12" s="1">
         <v>18</v>
       </c>
-      <c r="B12" s="3" t="str">
+      <c r="B12" s="4" t="str">
         <f t="shared" si="0"/>
         <v>18MS14-1071_POWDEREDROSE</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="D12" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H12">
+      <c r="F12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" s="1">
         <v>1</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="1">
         <v>198</v>
       </c>
+      <c r="N12" s="6" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="13" customHeight="1" spans="1:15">
-      <c r="A13">
+      <c r="A13" s="1">
         <v>19</v>
       </c>
-      <c r="B13" s="3" t="str">
+      <c r="B13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>19MS14-1063_LIGHTGREY</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
+        <v>199</v>
+      </c>
+      <c r="N13" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="M13">
-        <v>199</v>
-      </c>
     </row>
     <row r="14" customHeight="1" spans="1:15">
-      <c r="A14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="3" t="str">
+      <c r="A14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="4" t="str">
         <f>A14&amp;D14&amp;"_"&amp;F14</f>
         <v>19_5MS14-1063_POWEREDROSESORBET</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1">
+        <v>200</v>
+      </c>
+      <c r="N14" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <v>200</v>
-      </c>
     </row>
     <row r="15" customHeight="1" spans="1:15">
-      <c r="A15">
+      <c r="A15" s="1">
         <v>20</v>
       </c>
-      <c r="B15" s="3" t="str">
+      <c r="B15" s="4" t="str">
         <f>A15&amp;D15&amp;"_"&amp;F15</f>
         <v>20MS14-1063_PINE</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="1">
+        <v>2</v>
+      </c>
+      <c r="N15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15">
-        <v>2</v>
-      </c>
     </row>
     <row r="16" customHeight="1" spans="1:15">
-      <c r="A16">
+      <c r="A16" s="1">
         <v>21</v>
       </c>
-      <c r="B16" s="3" t="str">
+      <c r="B16" s="4" t="str">
         <f>A16&amp;D16&amp;"_"&amp;F16</f>
         <v>21MS14-1069_LIGHTGREY</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="D16" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:8">
-      <c r="A17">
+      <c r="N16" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:14">
+      <c r="A17" s="1">
         <v>22</v>
       </c>
-      <c r="B17" s="3" t="str">
+      <c r="B17" s="4" t="str">
         <f>A17&amp;D17&amp;"_"&amp;F17</f>
         <v>22MS14-1069_POWDEREDROSESORBET</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="1" t="s">
+      <c r="D17" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="E17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:8">
-      <c r="A18">
+      <c r="N17" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:14">
+      <c r="A18" s="1">
         <v>23</v>
       </c>
-      <c r="B18" s="3" t="str">
+      <c r="B18" s="4" t="str">
         <f t="shared" ref="B17:B22" si="1">A18&amp;D18&amp;"_"&amp;F18</f>
         <v>23MS14-1069_PINE</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="D18" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:8">
-      <c r="A19">
+      <c r="N18" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:14">
+      <c r="A19" s="1">
         <v>24</v>
       </c>
-      <c r="B19" s="3" t="str">
+      <c r="B19" s="4" t="str">
         <f t="shared" si="1"/>
         <v>24MS14-1068_LIGHTGREY</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="F19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:8">
-      <c r="A20">
+      <c r="N19" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:14">
+      <c r="A20" s="1">
         <v>25</v>
       </c>
-      <c r="B20" s="3" t="str">
+      <c r="B20" s="4" t="str">
         <f t="shared" si="1"/>
         <v>25MS14-1068_PINE</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="F20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:8">
-      <c r="A21">
+      <c r="N20" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:14">
+      <c r="A21" s="1">
         <v>26</v>
       </c>
-      <c r="B21" s="3" t="str">
+      <c r="B21" s="4" t="str">
         <f t="shared" si="1"/>
         <v>26AS151101_BLACK</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="D21" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F21" t="s">
-        <v>51</v>
-      </c>
-      <c r="H21">
+      <c r="F21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H21" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:8">
-      <c r="A22">
+      <c r="N21" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:14">
+      <c r="A22" s="1">
         <v>27</v>
       </c>
-      <c r="B22" s="3" t="str">
+      <c r="B22" s="4" t="str">
         <f t="shared" si="1"/>
         <v>27AS151101_BLACK</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D22" t="s">
-        <v>50</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F22" t="s">
-        <v>51</v>
-      </c>
-      <c r="H22">
+      <c r="D22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H22" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:8">
-      <c r="A23">
+      <c r="N22" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:14">
+      <c r="A23" s="1">
         <v>28</v>
       </c>
-      <c r="B23" s="3" t="str">
+      <c r="B23" s="4" t="str">
         <f t="shared" ref="B23:B29" si="2">A23&amp;D23&amp;"_"&amp;F23</f>
         <v>28MS141070_LIGHTGREY</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D23" t="s">
-        <v>53</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="D23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:8">
-      <c r="A24">
+      <c r="N23" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:14">
+      <c r="A24" s="1">
         <v>29</v>
       </c>
-      <c r="B24" s="3" t="str">
+      <c r="B24" s="4" t="str">
         <f t="shared" si="2"/>
         <v>29AS151003_GREYMELANGE+DKBLUEDIP</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F24" s="1" t="s">
+      <c r="D24" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:8">
-      <c r="A25">
+      <c r="N24" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:14">
+      <c r="A25" s="1">
         <v>30</v>
       </c>
-      <c r="B25" s="3" t="str">
+      <c r="B25" s="4" t="str">
         <f t="shared" si="2"/>
         <v>30MS14-1066_SORBET</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H25">
+      <c r="D25" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H25" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:8">
-      <c r="A26">
+      <c r="N25" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:14">
+      <c r="A26" s="1">
         <v>31</v>
       </c>
-      <c r="B26" s="3" t="str">
+      <c r="B26" s="4" t="str">
         <f t="shared" si="2"/>
         <v>31MS14-1066_LIGHTGREY</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="D26" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:8">
-      <c r="A27">
+      <c r="N26" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:14">
+      <c r="A27" s="1">
         <v>32</v>
       </c>
-      <c r="B27" s="3" t="str">
+      <c r="B27" s="4" t="str">
         <f t="shared" si="2"/>
         <v>32MS14-1074_POWDEREROSE</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H27">
+      <c r="D27" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H27" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:8">
-      <c r="A28">
+      <c r="N27" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:14">
+      <c r="A28" s="1">
         <v>33</v>
       </c>
-      <c r="B28" s="3" t="str">
+      <c r="B28" s="4" t="str">
         <f t="shared" si="2"/>
         <v>33MS14-1061_SORBET</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H28">
+      <c r="D28" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H28" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:8">
-      <c r="A29">
+      <c r="N28" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:14">
+      <c r="A29" s="1">
         <v>34</v>
       </c>
-      <c r="B29" s="3" t="str">
+      <c r="B29" s="4" t="str">
         <f t="shared" si="2"/>
         <v>34MS14-1061_CLOUD</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="D29" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:8">
-      <c r="A30">
+      <c r="N29" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:14">
+      <c r="A30" s="1">
         <v>35</v>
       </c>
-      <c r="B30" s="3" t="str">
+      <c r="B30" s="4" t="str">
         <f t="shared" ref="B30:B36" si="3">A30&amp;D30&amp;"_"&amp;F30</f>
         <v>35MS14-1061_PINE</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F30" s="5" t="s">
+      <c r="D30" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:8">
-      <c r="A31">
+      <c r="N30" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:14">
+      <c r="A31" s="1">
         <v>36</v>
       </c>
-      <c r="B31" s="3" t="str">
+      <c r="B31" s="4" t="str">
         <f t="shared" si="3"/>
         <v>36MS14-1073_POWDEREDROSE</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H31">
+      <c r="D31" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H31" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" customHeight="1" spans="1:8">
-      <c r="A32">
+      <c r="N31" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:14">
+      <c r="A32" s="1">
         <v>37</v>
       </c>
-      <c r="B32" s="3" t="str">
+      <c r="B32" s="4" t="str">
         <f t="shared" si="3"/>
         <v>37MS14-1073_LIGHTGREYCLOUD</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D32" t="s">
-        <v>63</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H32">
+      <c r="D32" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H32" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" customHeight="1" spans="1:8">
-      <c r="A33">
+      <c r="N32" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:14">
+      <c r="A33" s="1">
         <v>38</v>
       </c>
-      <c r="B33" s="3" t="str">
+      <c r="B33" s="4" t="str">
         <f t="shared" si="3"/>
         <v>38MS14-1073_PINE</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D33" t="s">
-        <v>63</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F33" s="5" t="s">
+      <c r="D33" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F33" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" customHeight="1" spans="1:8">
-      <c r="A34">
+      <c r="N33" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:14">
+      <c r="A34" s="1">
         <v>39</v>
       </c>
-      <c r="B34" s="3" t="str">
+      <c r="B34" s="4" t="str">
         <f t="shared" si="3"/>
         <v>39MS14-1060_LTGREYCLOUD</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F34" s="1" t="s">
+      <c r="D34" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H34" s="1">
+        <v>1</v>
+      </c>
+      <c r="N34" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="H34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="1:8">
-      <c r="A35">
+    </row>
+    <row r="35" customHeight="1" spans="1:14">
+      <c r="A35" s="1">
         <v>40</v>
       </c>
-      <c r="B35" s="3" t="str">
+      <c r="B35" s="4" t="str">
         <f t="shared" si="3"/>
         <v>40MS14-1060_POWDEREDROSE</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H35">
+      <c r="D35" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H35" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" customHeight="1" spans="1:8">
-      <c r="A36">
+      <c r="N35" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:14">
+      <c r="A36" s="1">
         <v>41</v>
       </c>
-      <c r="B36" s="3" t="str">
+      <c r="B36" s="4" t="str">
         <f t="shared" si="3"/>
         <v>41MS14-1060_PINE</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F36" s="5" t="s">
+      <c r="D36" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F36" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" customHeight="1" spans="1:8">
-      <c r="A37">
+      <c r="N36" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:14">
+      <c r="A37" s="1">
         <v>42</v>
       </c>
-      <c r="B37" s="3"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:8">
-      <c r="B38" s="3"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:8">
-      <c r="B39" s="3"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:8">
-      <c r="B40" s="3"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:8">
-      <c r="B41" s="3"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:8">
-      <c r="B42" s="3"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:8">
-      <c r="B43" s="3"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:8">
-      <c r="B44" s="3"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:8">
-      <c r="B45" s="3"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:8">
-      <c r="B46" s="3"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:8">
-      <c r="B47" s="3"/>
-    </row>
-    <row r="48" customHeight="1" spans="1:8">
-      <c r="B48" s="3"/>
+      <c r="B37" s="4"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:14">
+      <c r="B38" s="4"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:14">
+      <c r="B39" s="4"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:14">
+      <c r="B40" s="4"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:14">
+      <c r="B41" s="4"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:14">
+      <c r="B42" s="4"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:14">
+      <c r="B43" s="4"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:14">
+      <c r="B44" s="4"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:14">
+      <c r="B45" s="4"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:14">
+      <c r="B46" s="4"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:14">
+      <c r="B47" s="4"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:14">
+      <c r="B48" s="4"/>
     </row>
     <row r="49" customHeight="1" spans="2:2">
-      <c r="B49" s="3"/>
+      <c r="B49" s="4"/>
     </row>
     <row r="50" customHeight="1" spans="2:2">
-      <c r="B50" s="3"/>
+      <c r="B50" s="4"/>
     </row>
     <row r="51" customHeight="1" spans="2:2">
-      <c r="B51" s="3"/>
+      <c r="B51" s="4"/>
     </row>
     <row r="52" customHeight="1" spans="2:2">
-      <c r="B52" s="3"/>
+      <c r="B52" s="4"/>
     </row>
     <row r="53" customHeight="1" spans="2:2">
-      <c r="B53" s="3"/>
+      <c r="B53" s="4"/>
     </row>
     <row r="54" customHeight="1" spans="2:2">
-      <c r="B54" s="3"/>
+      <c r="B54" s="4"/>
     </row>
     <row r="55" customHeight="1" spans="2:2">
-      <c r="B55" s="3"/>
+      <c r="B55" s="4"/>
     </row>
     <row r="56" customHeight="1" spans="2:2">
-      <c r="B56" s="3"/>
+      <c r="B56" s="4"/>
     </row>
     <row r="57" customHeight="1" spans="2:2">
-      <c r="B57" s="3"/>
+      <c r="B57" s="4"/>
     </row>
     <row r="58" customHeight="1" spans="2:2">
-      <c r="B58" s="3"/>
+      <c r="B58" s="4"/>
     </row>
     <row r="59" customHeight="1" spans="2:2">
-      <c r="B59" s="3"/>
+      <c r="B59" s="4"/>
     </row>
     <row r="60" customHeight="1" spans="2:2">
-      <c r="B60" s="3"/>
+      <c r="B60" s="4"/>
     </row>
     <row r="61" customHeight="1" spans="2:2">
-      <c r="B61" s="3"/>
+      <c r="B61" s="4"/>
     </row>
     <row r="62" customHeight="1" spans="2:2">
-      <c r="B62" s="3"/>
+      <c r="B62" s="4"/>
     </row>
     <row r="63" customHeight="1" spans="2:2">
-      <c r="B63" s="3"/>
+      <c r="B63" s="4"/>
     </row>
     <row r="64" customHeight="1" spans="2:2">
-      <c r="B64" s="3"/>
+      <c r="B64" s="4"/>
     </row>
     <row r="65" customHeight="1" spans="2:2">
-      <c r="B65" s="3"/>
+      <c r="B65" s="4"/>
     </row>
     <row r="66" customHeight="1" spans="2:2">
-      <c r="B66" s="3"/>
+      <c r="B66" s="4"/>
     </row>
     <row r="67" customHeight="1" spans="2:2">
-      <c r="B67" s="3"/>
+      <c r="B67" s="4"/>
     </row>
     <row r="68" customHeight="1" spans="2:2">
-      <c r="B68" s="3"/>
+      <c r="B68" s="4"/>
     </row>
     <row r="69" customHeight="1" spans="2:2">
-      <c r="B69" s="3"/>
+      <c r="B69" s="4"/>
     </row>
     <row r="70" customHeight="1" spans="2:2">
-      <c r="B70" s="3"/>
+      <c r="B70" s="4"/>
     </row>
     <row r="71" customHeight="1" spans="2:2">
-      <c r="B71" s="3"/>
+      <c r="B71" s="4"/>
     </row>
     <row r="72" customHeight="1" spans="2:2">
-      <c r="B72" s="3"/>
+      <c r="B72" s="4"/>
     </row>
     <row r="73" customHeight="1" spans="2:2">
-      <c r="B73" s="3"/>
+      <c r="B73" s="4"/>
     </row>
     <row r="74" customHeight="1" spans="2:2">
-      <c r="B74" s="3"/>
+      <c r="B74" s="4"/>
     </row>
     <row r="75" customHeight="1" spans="2:2">
-      <c r="B75" s="3"/>
+      <c r="B75" s="4"/>
     </row>
     <row r="76" customHeight="1" spans="2:2">
-      <c r="B76" s="3"/>
+      <c r="B76" s="4"/>
     </row>
     <row r="77" customHeight="1" spans="2:2">
-      <c r="B77" s="3"/>
+      <c r="B77" s="4"/>
     </row>
     <row r="78" customHeight="1" spans="2:2">
-      <c r="B78" s="3"/>
+      <c r="B78" s="4"/>
     </row>
     <row r="79" customHeight="1" spans="2:2">
-      <c r="B79" s="3"/>
+      <c r="B79" s="4"/>
     </row>
     <row r="80" customHeight="1" spans="2:2">
-      <c r="B80" s="3"/>
+      <c r="B80" s="4"/>
     </row>
     <row r="81" customHeight="1" spans="2:2">
-      <c r="B81" s="3"/>
+      <c r="B81" s="4"/>
     </row>
     <row r="82" customHeight="1" spans="2:2">
-      <c r="B82" s="3"/>
+      <c r="B82" s="4"/>
     </row>
     <row r="83" customHeight="1" spans="2:2">
-      <c r="B83" s="3"/>
+      <c r="B83" s="4"/>
     </row>
     <row r="84" customHeight="1" spans="2:2">
-      <c r="B84" s="3"/>
+      <c r="B84" s="4"/>
     </row>
     <row r="85" customHeight="1" spans="2:2">
-      <c r="B85" s="3"/>
+      <c r="B85" s="4"/>
     </row>
     <row r="86" customHeight="1" spans="2:2">
-      <c r="B86" s="3"/>
+      <c r="B86" s="4"/>
     </row>
     <row r="87" customHeight="1" spans="2:2">
-      <c r="B87" s="3"/>
+      <c r="B87" s="4"/>
     </row>
     <row r="88" customHeight="1" spans="2:2">
-      <c r="B88" s="3"/>
+      <c r="B88" s="4"/>
     </row>
     <row r="89" customHeight="1" spans="2:2">
-      <c r="B89" s="3"/>
+      <c r="B89" s="4"/>
     </row>
     <row r="90" customHeight="1" spans="2:2">
-      <c r="B90" s="3"/>
+      <c r="B90" s="4"/>
     </row>
     <row r="91" customHeight="1" spans="2:2">
-      <c r="B91" s="3"/>
+      <c r="B91" s="4"/>
     </row>
     <row r="92" customHeight="1" spans="2:2">
-      <c r="B92" s="3"/>
+      <c r="B92" s="4"/>
     </row>
     <row r="93" customHeight="1" spans="2:2">
-      <c r="B93" s="3"/>
+      <c r="B93" s="4"/>
     </row>
     <row r="94" customHeight="1" spans="2:2">
-      <c r="B94" s="3"/>
+      <c r="B94" s="4"/>
     </row>
     <row r="95" customHeight="1" spans="2:2">
-      <c r="B95" s="3"/>
+      <c r="B95" s="4"/>
     </row>
     <row r="96" customHeight="1" spans="2:2">
-      <c r="B96" s="3"/>
+      <c r="B96" s="4"/>
     </row>
     <row r="97" customHeight="1" spans="2:2">
-      <c r="B97" s="3"/>
+      <c r="B97" s="4"/>
     </row>
     <row r="98" customHeight="1" spans="2:2">
-      <c r="B98" s="3"/>
+      <c r="B98" s="4"/>
     </row>
     <row r="99" customHeight="1" spans="2:2">
-      <c r="B99" s="3"/>
+      <c r="B99" s="4"/>
     </row>
     <row r="100" customHeight="1" spans="2:2">
-      <c r="B100" s="3"/>
+      <c r="B100" s="4"/>
     </row>
     <row r="101" customHeight="1" spans="2:2">
-      <c r="B101" s="3"/>
+      <c r="B101" s="4"/>
     </row>
     <row r="102" customHeight="1" spans="2:2">
-      <c r="B102" s="3"/>
+      <c r="B102" s="4"/>
     </row>
     <row r="103" customHeight="1" spans="2:2">
-      <c r="B103" s="3"/>
+      <c r="B103" s="4"/>
     </row>
     <row r="104" customHeight="1" spans="2:2">
-      <c r="B104" s="3"/>
+      <c r="B104" s="4"/>
     </row>
     <row r="105" customHeight="1" spans="2:2">
-      <c r="B105" s="3"/>
+      <c r="B105" s="4"/>
     </row>
     <row r="106" customHeight="1" spans="2:2">
-      <c r="B106" s="3"/>
+      <c r="B106" s="4"/>
     </row>
     <row r="107" customHeight="1" spans="2:2">
-      <c r="B107" s="3"/>
+      <c r="B107" s="4"/>
     </row>
     <row r="108" customHeight="1" spans="2:2">
-      <c r="B108" s="3"/>
+      <c r="B108" s="4"/>
     </row>
     <row r="109" customHeight="1" spans="2:2">
-      <c r="B109" s="3"/>
+      <c r="B109" s="4"/>
     </row>
     <row r="110" customHeight="1" spans="2:2">
-      <c r="B110" s="3"/>
+      <c r="B110" s="4"/>
     </row>
     <row r="111" customHeight="1" spans="2:2">
-      <c r="B111" s="3"/>
+      <c r="B111" s="4"/>
     </row>
     <row r="112" customHeight="1" spans="2:2">
-      <c r="B112" s="3"/>
+      <c r="B112" s="4"/>
     </row>
     <row r="113" customHeight="1" spans="2:2">
-      <c r="B113" s="3"/>
+      <c r="B113" s="4"/>
     </row>
     <row r="114" customHeight="1" spans="2:2">
-      <c r="B114" s="3"/>
+      <c r="B114" s="4"/>
     </row>
     <row r="115" customHeight="1" spans="2:2">
-      <c r="B115" s="3"/>
+      <c r="B115" s="4"/>
     </row>
     <row r="116" customHeight="1" spans="2:2">
-      <c r="B116" s="3"/>
+      <c r="B116" s="4"/>
     </row>
     <row r="117" customHeight="1" spans="2:2">
-      <c r="B117" s="3"/>
+      <c r="B117" s="4"/>
     </row>
     <row r="118" customHeight="1" spans="2:2">
-      <c r="B118" s="3"/>
+      <c r="B118" s="4"/>
     </row>
     <row r="119" customHeight="1" spans="2:2">
-      <c r="B119" s="3"/>
+      <c r="B119" s="4"/>
     </row>
     <row r="120" customHeight="1" spans="2:2">
-      <c r="B120" s="3"/>
+      <c r="B120" s="4"/>
     </row>
     <row r="121" customHeight="1" spans="2:2">
-      <c r="B121" s="3"/>
+      <c r="B121" s="4"/>
     </row>
     <row r="122" customHeight="1" spans="2:2">
-      <c r="B122" s="3"/>
+      <c r="B122" s="4"/>
     </row>
     <row r="123" customHeight="1" spans="2:2">
-      <c r="B123" s="3"/>
+      <c r="B123" s="4"/>
     </row>
     <row r="124" customHeight="1" spans="2:2">
-      <c r="B124" s="3"/>
+      <c r="B124" s="4"/>
     </row>
     <row r="125" customHeight="1" spans="2:2">
-      <c r="B125" s="3"/>
+      <c r="B125" s="4"/>
     </row>
     <row r="126" customHeight="1" spans="2:2">
-      <c r="B126" s="3"/>
+      <c r="B126" s="4"/>
     </row>
     <row r="127" customHeight="1" spans="2:2">
-      <c r="B127" s="3"/>
+      <c r="B127" s="4"/>
     </row>
     <row r="128" customHeight="1" spans="2:2">
-      <c r="B128" s="3"/>
+      <c r="B128" s="4"/>
     </row>
     <row r="129" customHeight="1" spans="2:2">
-      <c r="B129" s="3"/>
+      <c r="B129" s="4"/>
     </row>
     <row r="130" customHeight="1" spans="2:2">
-      <c r="B130" s="3"/>
+      <c r="B130" s="4"/>
     </row>
     <row r="131" customHeight="1" spans="2:2">
-      <c r="B131" s="3"/>
+      <c r="B131" s="4"/>
     </row>
     <row r="132" customHeight="1" spans="2:2">
-      <c r="B132" s="3"/>
+      <c r="B132" s="4"/>
     </row>
     <row r="133" customHeight="1" spans="2:2">
-      <c r="B133" s="3"/>
+      <c r="B133" s="4"/>
     </row>
     <row r="134" customHeight="1" spans="2:2">
-      <c r="B134" s="3"/>
+      <c r="B134" s="4"/>
     </row>
     <row r="135" customHeight="1" spans="2:2">
-      <c r="B135" s="3"/>
+      <c r="B135" s="4"/>
     </row>
     <row r="136" customHeight="1" spans="2:2">
-      <c r="B136" s="3"/>
+      <c r="B136" s="4"/>
     </row>
     <row r="137" customHeight="1" spans="2:2">
-      <c r="B137" s="3"/>
+      <c r="B137" s="4"/>
     </row>
     <row r="138" customHeight="1" spans="2:2">
-      <c r="B138" s="3"/>
+      <c r="B138" s="4"/>
     </row>
     <row r="139" customHeight="1" spans="2:2">
-      <c r="B139" s="3"/>
+      <c r="B139" s="4"/>
     </row>
     <row r="140" customHeight="1" spans="2:2">
-      <c r="B140" s="3"/>
+      <c r="B140" s="4"/>
     </row>
     <row r="141" customHeight="1" spans="2:2">
-      <c r="B141" s="3"/>
+      <c r="B141" s="4"/>
     </row>
     <row r="142" customHeight="1" spans="2:2">
-      <c r="B142" s="3"/>
+      <c r="B142" s="4"/>
     </row>
     <row r="143" customHeight="1" spans="2:2">
-      <c r="B143" s="3"/>
+      <c r="B143" s="4"/>
     </row>
     <row r="144" customHeight="1" spans="2:2">
-      <c r="B144" s="3"/>
+      <c r="B144" s="4"/>
     </row>
     <row r="145" customHeight="1" spans="2:2">
-      <c r="B145" s="3"/>
+      <c r="B145" s="4"/>
     </row>
     <row r="146" customHeight="1" spans="2:2">
-      <c r="B146" s="3"/>
+      <c r="B146" s="4"/>
     </row>
     <row r="147" customHeight="1" spans="2:2">
-      <c r="B147" s="3"/>
+      <c r="B147" s="4"/>
     </row>
     <row r="148" customHeight="1" spans="2:2">
-      <c r="B148" s="3"/>
+      <c r="B148" s="4"/>
     </row>
     <row r="149" customHeight="1" spans="2:2">
-      <c r="B149" s="3"/>
+      <c r="B149" s="4"/>
     </row>
     <row r="150" customHeight="1" spans="2:2">
-      <c r="B150" s="3"/>
+      <c r="B150" s="4"/>
     </row>
     <row r="151" customHeight="1" spans="2:2">
-      <c r="B151" s="3"/>
+      <c r="B151" s="4"/>
     </row>
     <row r="152" customHeight="1" spans="2:2">
-      <c r="B152" s="3"/>
+      <c r="B152" s="4"/>
     </row>
     <row r="153" customHeight="1" spans="2:2">
-      <c r="B153" s="3"/>
+      <c r="B153" s="4"/>
     </row>
     <row r="154" customHeight="1" spans="2:2">
-      <c r="B154" s="3"/>
+      <c r="B154" s="4"/>
     </row>
     <row r="155" customHeight="1" spans="2:2">
-      <c r="B155" s="3"/>
+      <c r="B155" s="4"/>
     </row>
     <row r="156" customHeight="1" spans="2:2">
-      <c r="B156" s="3"/>
+      <c r="B156" s="4"/>
     </row>
     <row r="157" customHeight="1" spans="2:2">
-      <c r="B157" s="3"/>
+      <c r="B157" s="4"/>
     </row>
     <row r="158" customHeight="1" spans="2:2">
-      <c r="B158" s="3"/>
+      <c r="B158" s="4"/>
     </row>
     <row r="159" customHeight="1" spans="2:2">
-      <c r="B159" s="3"/>
+      <c r="B159" s="4"/>
     </row>
     <row r="160" customHeight="1" spans="2:2">
-      <c r="B160" s="3"/>
+      <c r="B160" s="4"/>
     </row>
     <row r="161" customHeight="1" spans="2:2">
-      <c r="B161" s="3"/>
+      <c r="B161" s="4"/>
     </row>
     <row r="162" customHeight="1" spans="2:2">
-      <c r="B162" s="3"/>
+      <c r="B162" s="4"/>
     </row>
     <row r="163" customHeight="1" spans="2:2">
-      <c r="B163" s="3"/>
+      <c r="B163" s="4"/>
     </row>
     <row r="164" customHeight="1" spans="2:2">
-      <c r="B164" s="3"/>
+      <c r="B164" s="4"/>
     </row>
     <row r="165" customHeight="1" spans="2:2">
-      <c r="B165" s="3"/>
+      <c r="B165" s="4"/>
     </row>
     <row r="166" customHeight="1" spans="2:2">
-      <c r="B166" s="3"/>
+      <c r="B166" s="4"/>
     </row>
     <row r="167" customHeight="1" spans="2:2">
-      <c r="B167" s="3"/>
+      <c r="B167" s="4"/>
     </row>
     <row r="168" customHeight="1" spans="2:2">
-      <c r="B168" s="3"/>
+      <c r="B168" s="4"/>
     </row>
     <row r="169" customHeight="1" spans="2:2">
-      <c r="B169" s="3"/>
+      <c r="B169" s="4"/>
     </row>
     <row r="170" customHeight="1" spans="2:2">
-      <c r="B170" s="3"/>
+      <c r="B170" s="4"/>
     </row>
     <row r="171" customHeight="1" spans="2:2">
-      <c r="B171" s="3"/>
+      <c r="B171" s="4"/>
     </row>
     <row r="172" customHeight="1" spans="2:2">
-      <c r="B172" s="3"/>
+      <c r="B172" s="4"/>
     </row>
     <row r="173" customHeight="1" spans="2:2">
-      <c r="B173" s="3"/>
+      <c r="B173" s="4"/>
     </row>
     <row r="174" customHeight="1" spans="2:2">
-      <c r="B174" s="3"/>
+      <c r="B174" s="4"/>
     </row>
     <row r="175" customHeight="1" spans="2:2">
-      <c r="B175" s="3"/>
+      <c r="B175" s="4"/>
     </row>
     <row r="176" customHeight="1" spans="2:2">
-      <c r="B176" s="3"/>
+      <c r="B176" s="4"/>
     </row>
     <row r="177" customHeight="1" spans="2:2">
-      <c r="B177" s="3"/>
+      <c r="B177" s="4"/>
     </row>
     <row r="178" customHeight="1" spans="2:2">
-      <c r="B178" s="3"/>
+      <c r="B178" s="4"/>
     </row>
     <row r="179" customHeight="1" spans="2:2">
-      <c r="B179" s="3"/>
+      <c r="B179" s="4"/>
     </row>
     <row r="180" customHeight="1" spans="2:2">
-      <c r="B180" s="3"/>
+      <c r="B180" s="4"/>
     </row>
     <row r="181" customHeight="1" spans="2:2">
-      <c r="B181" s="3"/>
+      <c r="B181" s="4"/>
     </row>
     <row r="182" customHeight="1" spans="2:2">
-      <c r="B182" s="3"/>
+      <c r="B182" s="4"/>
     </row>
     <row r="183" customHeight="1" spans="2:2">
-      <c r="B183" s="3"/>
+      <c r="B183" s="4"/>
     </row>
     <row r="184" customHeight="1" spans="2:2">
-      <c r="B184" s="3"/>
+      <c r="B184" s="4"/>
     </row>
     <row r="185" customHeight="1" spans="2:2">
-      <c r="B185" s="3"/>
+      <c r="B185" s="4"/>
     </row>
     <row r="186" customHeight="1" spans="2:2">
-      <c r="B186" s="3"/>
+      <c r="B186" s="4"/>
     </row>
     <row r="187" customHeight="1" spans="2:2">
-      <c r="B187" s="3"/>
+      <c r="B187" s="4"/>
     </row>
     <row r="188" customHeight="1" spans="2:2">
-      <c r="B188" s="3"/>
+      <c r="B188" s="4"/>
     </row>
     <row r="189" customHeight="1" spans="2:2">
-      <c r="B189" s="3"/>
+      <c r="B189" s="4"/>
     </row>
     <row r="190" customHeight="1" spans="2:2">
-      <c r="B190" s="3"/>
+      <c r="B190" s="4"/>
     </row>
     <row r="191" customHeight="1" spans="2:2">
-      <c r="B191" s="3"/>
+      <c r="B191" s="4"/>
     </row>
     <row r="192" customHeight="1" spans="2:2">
-      <c r="B192" s="3"/>
+      <c r="B192" s="4"/>
     </row>
     <row r="193" customHeight="1" spans="2:2">
-      <c r="B193" s="3"/>
+      <c r="B193" s="4"/>
     </row>
     <row r="194" customHeight="1" spans="2:2">
-      <c r="B194" s="3"/>
+      <c r="B194" s="4"/>
     </row>
     <row r="195" customHeight="1" spans="2:2">
-      <c r="B195" s="3"/>
+      <c r="B195" s="4"/>
     </row>
     <row r="196" customHeight="1" spans="2:2">
-      <c r="B196" s="3"/>
+      <c r="B196" s="4"/>
     </row>
     <row r="197" customHeight="1" spans="2:2">
-      <c r="B197" s="3"/>
+      <c r="B197" s="4"/>
     </row>
     <row r="198" customHeight="1" spans="2:2">
-      <c r="B198" s="3"/>
+      <c r="B198" s="4"/>
     </row>
     <row r="199" customHeight="1" spans="2:2">
-      <c r="B199" s="3"/>
+      <c r="B199" s="4"/>
     </row>
     <row r="200" customHeight="1" spans="2:2">
-      <c r="B200" s="3"/>
+      <c r="B200" s="4"/>
     </row>
     <row r="201" customHeight="1" spans="2:2">
-      <c r="B201" s="3"/>
+      <c r="B201" s="4"/>
     </row>
     <row r="202" customHeight="1" spans="2:2">
-      <c r="B202" s="3"/>
+      <c r="B202" s="4"/>
     </row>
     <row r="203" customHeight="1" spans="2:2">
-      <c r="B203" s="3"/>
+      <c r="B203" s="4"/>
     </row>
     <row r="204" customHeight="1" spans="2:2">
-      <c r="B204" s="3"/>
+      <c r="B204" s="4"/>
     </row>
     <row r="205" customHeight="1" spans="2:2">
-      <c r="B205" s="3"/>
+      <c r="B205" s="4"/>
     </row>
     <row r="206" customHeight="1" spans="2:2">
-      <c r="B206" s="3"/>
+      <c r="B206" s="4"/>
     </row>
     <row r="207" customHeight="1" spans="2:2">
-      <c r="B207" s="3"/>
+      <c r="B207" s="4"/>
     </row>
     <row r="208" customHeight="1" spans="2:2">
-      <c r="B208" s="3"/>
+      <c r="B208" s="4"/>
     </row>
     <row r="209" customHeight="1" spans="2:2">
-      <c r="B209" s="3"/>
+      <c r="B209" s="4"/>
     </row>
     <row r="210" customHeight="1" spans="2:2">
-      <c r="B210" s="3"/>
+      <c r="B210" s="4"/>
     </row>
     <row r="211" customHeight="1" spans="2:2">
-      <c r="B211" s="3"/>
+      <c r="B211" s="4"/>
     </row>
     <row r="212" customHeight="1" spans="2:2">
-      <c r="B212" s="3"/>
+      <c r="B212" s="4"/>
     </row>
     <row r="213" customHeight="1" spans="2:2">
-      <c r="B213" s="3"/>
+      <c r="B213" s="4"/>
     </row>
     <row r="214" customHeight="1" spans="2:2">
-      <c r="B214" s="3"/>
+      <c r="B214" s="4"/>
     </row>
     <row r="215" customHeight="1" spans="2:2">
-      <c r="B215" s="3"/>
+      <c r="B215" s="4"/>
     </row>
     <row r="216" customHeight="1" spans="2:2">
-      <c r="B216" s="3"/>
+      <c r="B216" s="4"/>
     </row>
     <row r="217" customHeight="1" spans="2:2">
-      <c r="B217" s="3"/>
+      <c r="B217" s="4"/>
     </row>
     <row r="218" customHeight="1" spans="2:2">
-      <c r="B218" s="3"/>
+      <c r="B218" s="4"/>
     </row>
     <row r="219" customHeight="1" spans="2:2">
-      <c r="B219" s="3"/>
+      <c r="B219" s="4"/>
     </row>
     <row r="220" customHeight="1" spans="2:2">
-      <c r="B220" s="3"/>
+      <c r="B220" s="4"/>
     </row>
     <row r="221" customHeight="1" spans="2:2">
-      <c r="B221" s="3"/>
+      <c r="B221" s="4"/>
     </row>
     <row r="222" customHeight="1" spans="2:2">
-      <c r="B222" s="3"/>
+      <c r="B222" s="4"/>
     </row>
     <row r="223" customHeight="1" spans="2:2">
-      <c r="B223" s="3"/>
+      <c r="B223" s="4"/>
     </row>
     <row r="224" customHeight="1" spans="2:2">
-      <c r="B224" s="3"/>
+      <c r="B224" s="4"/>
     </row>
     <row r="225" customHeight="1" spans="2:2">
-      <c r="B225" s="3"/>
+      <c r="B225" s="4"/>
     </row>
     <row r="226" customHeight="1" spans="2:2">
-      <c r="B226" s="3"/>
+      <c r="B226" s="4"/>
     </row>
     <row r="227" customHeight="1" spans="2:2">
-      <c r="B227" s="3"/>
+      <c r="B227" s="4"/>
     </row>
     <row r="228" customHeight="1" spans="2:2">
-      <c r="B228" s="3"/>
+      <c r="B228" s="4"/>
     </row>
     <row r="229" customHeight="1" spans="2:2">
-      <c r="B229" s="3"/>
+      <c r="B229" s="4"/>
     </row>
     <row r="230" customHeight="1" spans="2:2">
-      <c r="B230" s="3"/>
+      <c r="B230" s="4"/>
     </row>
     <row r="231" customHeight="1" spans="2:2">
-      <c r="B231" s="3"/>
+      <c r="B231" s="4"/>
     </row>
     <row r="232" customHeight="1" spans="2:2">
-      <c r="B232" s="3"/>
+      <c r="B232" s="4"/>
     </row>
     <row r="233" customHeight="1" spans="2:2">
-      <c r="B233" s="3"/>
+      <c r="B233" s="4"/>
     </row>
     <row r="234" customHeight="1" spans="2:2">
-      <c r="B234" s="3"/>
+      <c r="B234" s="4"/>
     </row>
     <row r="235" customHeight="1" spans="2:2">
-      <c r="B235" s="3"/>
+      <c r="B235" s="4"/>
     </row>
     <row r="236" customHeight="1" spans="2:2">
-      <c r="B236" s="3"/>
+      <c r="B236" s="4"/>
     </row>
     <row r="237" customHeight="1" spans="2:2">
-      <c r="B237" s="3"/>
+      <c r="B237" s="4"/>
     </row>
     <row r="238" customHeight="1" spans="2:2">
-      <c r="B238" s="3"/>
+      <c r="B238" s="4"/>
     </row>
     <row r="239" customHeight="1" spans="2:2">
-      <c r="B239" s="3"/>
+      <c r="B239" s="4"/>
     </row>
     <row r="240" customHeight="1" spans="2:2">
-      <c r="B240" s="3"/>
+      <c r="B240" s="4"/>
     </row>
     <row r="241" customHeight="1" spans="2:2">
-      <c r="B241" s="3"/>
+      <c r="B241" s="4"/>
     </row>
     <row r="242" customHeight="1" spans="2:2">
-      <c r="B242" s="3"/>
+      <c r="B242" s="4"/>
     </row>
     <row r="243" customHeight="1" spans="2:2">
-      <c r="B243" s="3"/>
+      <c r="B243" s="4"/>
     </row>
     <row r="244" customHeight="1" spans="2:2">
-      <c r="B244" s="3"/>
+      <c r="B244" s="4"/>
     </row>
     <row r="245" customHeight="1" spans="2:2">
-      <c r="B245" s="3"/>
+      <c r="B245" s="4"/>
     </row>
     <row r="246" customHeight="1" spans="2:2">
-      <c r="B246" s="3"/>
+      <c r="B246" s="4"/>
     </row>
     <row r="247" customHeight="1" spans="2:2">
-      <c r="B247" s="3"/>
+      <c r="B247" s="4"/>
     </row>
     <row r="248" customHeight="1" spans="2:2">
-      <c r="B248" s="3"/>
+      <c r="B248" s="4"/>
     </row>
     <row r="249" customHeight="1" spans="2:2">
-      <c r="B249" s="3"/>
+      <c r="B249" s="4"/>
     </row>
     <row r="250" customHeight="1" spans="2:2">
-      <c r="B250" s="3"/>
+      <c r="B250" s="4"/>
     </row>
     <row r="251" customHeight="1" spans="2:2">
-      <c r="B251" s="3"/>
+      <c r="B251" s="4"/>
     </row>
     <row r="252" customHeight="1" spans="2:2">
-      <c r="B252" s="3"/>
+      <c r="B252" s="4"/>
     </row>
     <row r="253" customHeight="1" spans="2:2">
-      <c r="B253" s="3"/>
+      <c r="B253" s="4"/>
     </row>
     <row r="254" customHeight="1" spans="2:2">
-      <c r="B254" s="3"/>
+      <c r="B254" s="4"/>
     </row>
     <row r="255" customHeight="1" spans="2:2">
-      <c r="B255" s="3"/>
+      <c r="B255" s="4"/>
     </row>
     <row r="256" customHeight="1" spans="2:2">
-      <c r="B256" s="3"/>
+      <c r="B256" s="4"/>
     </row>
     <row r="257" customHeight="1" spans="2:2">
-      <c r="B257" s="3"/>
+      <c r="B257" s="4"/>
     </row>
     <row r="258" customHeight="1" spans="2:2">
-      <c r="B258" s="3"/>
+      <c r="B258" s="4"/>
     </row>
     <row r="259" customHeight="1" spans="2:2">
-      <c r="B259" s="3"/>
+      <c r="B259" s="4"/>
     </row>
     <row r="260" customHeight="1" spans="2:2">
-      <c r="B260" s="3"/>
+      <c r="B260" s="4"/>
     </row>
     <row r="261" customHeight="1" spans="2:2">
-      <c r="B261" s="3"/>
+      <c r="B261" s="4"/>
     </row>
     <row r="262" customHeight="1" spans="2:2">
-      <c r="B262" s="3"/>
+      <c r="B262" s="4"/>
     </row>
     <row r="263" customHeight="1" spans="2:2">
-      <c r="B263" s="3"/>
+      <c r="B263" s="4"/>
     </row>
     <row r="264" customHeight="1" spans="2:2">
-      <c r="B264" s="3"/>
+      <c r="B264" s="4"/>
     </row>
     <row r="265" customHeight="1" spans="2:2">
-      <c r="B265" s="3"/>
+      <c r="B265" s="4"/>
     </row>
     <row r="266" customHeight="1" spans="2:2">
-      <c r="B266" s="3"/>
+      <c r="B266" s="4"/>
     </row>
     <row r="267" customHeight="1" spans="2:2">
-      <c r="B267" s="3"/>
+      <c r="B267" s="4"/>
     </row>
     <row r="268" customHeight="1" spans="2:2">
-      <c r="B268" s="3"/>
+      <c r="B268" s="4"/>
     </row>
     <row r="269" customHeight="1" spans="2:2">
-      <c r="B269" s="3"/>
+      <c r="B269" s="4"/>
     </row>
     <row r="270" customHeight="1" spans="2:2">
-      <c r="B270" s="3"/>
+      <c r="B270" s="4"/>
     </row>
     <row r="271" customHeight="1" spans="2:2">
-      <c r="B271" s="3"/>
+      <c r="B271" s="4"/>
     </row>
     <row r="272" customHeight="1" spans="2:2">
-      <c r="B272" s="3"/>
+      <c r="B272" s="4"/>
     </row>
     <row r="273" customHeight="1" spans="2:2">
-      <c r="B273" s="3"/>
+      <c r="B273" s="4"/>
     </row>
     <row r="274" customHeight="1" spans="2:2">
-      <c r="B274" s="3"/>
+      <c r="B274" s="4"/>
     </row>
     <row r="275" customHeight="1" spans="2:2">
-      <c r="B275" s="3"/>
+      <c r="B275" s="4"/>
     </row>
     <row r="276" customHeight="1" spans="2:2">
-      <c r="B276" s="3"/>
+      <c r="B276" s="4"/>
     </row>
     <row r="277" customHeight="1" spans="2:2">
-      <c r="B277" s="3"/>
+      <c r="B277" s="4"/>
     </row>
     <row r="278" customHeight="1" spans="2:2">
-      <c r="B278" s="3"/>
+      <c r="B278" s="4"/>
     </row>
     <row r="279" customHeight="1" spans="2:2">
-      <c r="B279" s="3"/>
+      <c r="B279" s="4"/>
     </row>
     <row r="280" customHeight="1" spans="2:2">
-      <c r="B280" s="3"/>
+      <c r="B280" s="4"/>
     </row>
     <row r="281" customHeight="1" spans="2:2">
-      <c r="B281" s="3"/>
+      <c r="B281" s="4"/>
     </row>
     <row r="282" customHeight="1" spans="2:2">
-      <c r="B282" s="3"/>
+      <c r="B282" s="4"/>
     </row>
     <row r="283" customHeight="1" spans="2:2">
-      <c r="B283" s="3"/>
+      <c r="B283" s="4"/>
     </row>
     <row r="284" customHeight="1" spans="2:2">
-      <c r="B284" s="3"/>
+      <c r="B284" s="4"/>
     </row>
     <row r="285" customHeight="1" spans="2:2">
-      <c r="B285" s="3"/>
+      <c r="B285" s="4"/>
     </row>
     <row r="286" customHeight="1" spans="2:2">
-      <c r="B286" s="3"/>
+      <c r="B286" s="4"/>
     </row>
     <row r="287" customHeight="1" spans="2:2">
-      <c r="B287" s="3"/>
+      <c r="B287" s="4"/>
     </row>
     <row r="288" customHeight="1" spans="2:2">
-      <c r="B288" s="3"/>
+      <c r="B288" s="4"/>
     </row>
     <row r="289" customHeight="1" spans="2:2">
-      <c r="B289" s="3"/>
+      <c r="B289" s="4"/>
     </row>
     <row r="290" customHeight="1" spans="2:2">
-      <c r="B290" s="3"/>
+      <c r="B290" s="4"/>
     </row>
     <row r="291" customHeight="1" spans="2:2">
-      <c r="B291" s="3"/>
+      <c r="B291" s="4"/>
     </row>
     <row r="292" customHeight="1" spans="2:2">
-      <c r="B292" s="3"/>
+      <c r="B292" s="4"/>
     </row>
     <row r="293" customHeight="1" spans="2:2">
-      <c r="B293" s="3"/>
+      <c r="B293" s="4"/>
     </row>
     <row r="294" customHeight="1" spans="2:2">
-      <c r="B294" s="3"/>
+      <c r="B294" s="4"/>
     </row>
     <row r="295" customHeight="1" spans="2:2">
-      <c r="B295" s="3"/>
+      <c r="B295" s="4"/>
     </row>
     <row r="296" customHeight="1" spans="2:2">
-      <c r="B296" s="3"/>
+      <c r="B296" s="4"/>
     </row>
     <row r="297" customHeight="1" spans="2:2">
-      <c r="B297" s="3"/>
+      <c r="B297" s="4"/>
     </row>
     <row r="298" customHeight="1" spans="2:2">
-      <c r="B298" s="3"/>
+      <c r="B298" s="4"/>
     </row>
     <row r="299" customHeight="1" spans="2:2">
-      <c r="B299" s="3"/>
+      <c r="B299" s="4"/>
     </row>
     <row r="300" customHeight="1" spans="2:2">
-      <c r="B300" s="3"/>
+      <c r="B300" s="4"/>
     </row>
     <row r="301" customHeight="1" spans="2:2">
-      <c r="B301" s="3"/>
+      <c r="B301" s="4"/>
     </row>
     <row r="302" customHeight="1" spans="2:2">
-      <c r="B302" s="3"/>
+      <c r="B302" s="4"/>
     </row>
     <row r="303" customHeight="1" spans="2:2">
-      <c r="B303" s="3"/>
+      <c r="B303" s="4"/>
     </row>
     <row r="304" customHeight="1" spans="2:2">
-      <c r="B304" s="3"/>
+      <c r="B304" s="4"/>
     </row>
     <row r="305" customHeight="1" spans="2:2">
-      <c r="B305" s="3"/>
+      <c r="B305" s="4"/>
     </row>
     <row r="306" customHeight="1" spans="2:2">
-      <c r="B306" s="3"/>
+      <c r="B306" s="4"/>
     </row>
     <row r="307" customHeight="1" spans="2:2">
-      <c r="B307" s="3"/>
+      <c r="B307" s="4"/>
     </row>
     <row r="308" customHeight="1" spans="2:2">
-      <c r="B308" s="3"/>
+      <c r="B308" s="4"/>
     </row>
     <row r="309" customHeight="1" spans="2:2">
-      <c r="B309" s="3"/>
+      <c r="B309" s="4"/>
     </row>
     <row r="310" customHeight="1" spans="2:2">
-      <c r="B310" s="3"/>
+      <c r="B310" s="4"/>
     </row>
     <row r="311" customHeight="1" spans="2:2">
-      <c r="B311" s="3"/>
+      <c r="B311" s="4"/>
     </row>
     <row r="312" customHeight="1" spans="2:2">
-      <c r="B312" s="3"/>
+      <c r="B312" s="4"/>
     </row>
     <row r="313" customHeight="1" spans="2:2">
-      <c r="B313" s="3"/>
+      <c r="B313" s="4"/>
     </row>
     <row r="314" customHeight="1" spans="2:2">
-      <c r="B314" s="3"/>
+      <c r="B314" s="4"/>
     </row>
     <row r="315" customHeight="1" spans="2:2">
-      <c r="B315" s="3"/>
+      <c r="B315" s="4"/>
     </row>
     <row r="316" customHeight="1" spans="2:2">
-      <c r="B316" s="3"/>
+      <c r="B316" s="4"/>
     </row>
     <row r="317" customHeight="1" spans="2:2">
-      <c r="B317" s="3"/>
+      <c r="B317" s="4"/>
     </row>
     <row r="318" customHeight="1" spans="2:2">
-      <c r="B318" s="3"/>
+      <c r="B318" s="4"/>
     </row>
     <row r="319" customHeight="1" spans="2:2">
-      <c r="B319" s="3"/>
+      <c r="B319" s="4"/>
     </row>
     <row r="320" customHeight="1" spans="2:2">
-      <c r="B320" s="3"/>
+      <c r="B320" s="4"/>
     </row>
     <row r="321" customHeight="1" spans="2:2">
-      <c r="B321" s="3"/>
+      <c r="B321" s="4"/>
     </row>
     <row r="322" customHeight="1" spans="2:2">
-      <c r="B322" s="3"/>
+      <c r="B322" s="4"/>
     </row>
     <row r="323" customHeight="1" spans="2:2">
-      <c r="B323" s="3"/>
+      <c r="B323" s="4"/>
     </row>
     <row r="324" customHeight="1" spans="2:2">
-      <c r="B324" s="3"/>
+      <c r="B324" s="4"/>
     </row>
     <row r="325" customHeight="1" spans="2:2">
-      <c r="B325" s="3"/>
+      <c r="B325" s="4"/>
     </row>
     <row r="326" customHeight="1" spans="2:2">
-      <c r="B326" s="3"/>
+      <c r="B326" s="4"/>
     </row>
     <row r="327" customHeight="1" spans="2:2">
-      <c r="B327" s="3"/>
+      <c r="B327" s="4"/>
     </row>
     <row r="328" customHeight="1" spans="2:2">
-      <c r="B328" s="3"/>
+      <c r="B328" s="4"/>
     </row>
     <row r="329" customHeight="1" spans="2:2">
-      <c r="B329" s="3"/>
+      <c r="B329" s="4"/>
     </row>
     <row r="330" customHeight="1" spans="2:2">
-      <c r="B330" s="3"/>
+      <c r="B330" s="4"/>
     </row>
     <row r="331" customHeight="1" spans="2:2">
-      <c r="B331" s="3"/>
+      <c r="B331" s="4"/>
     </row>
     <row r="332" customHeight="1" spans="2:2">
-      <c r="B332" s="3"/>
+      <c r="B332" s="4"/>
     </row>
     <row r="333" customHeight="1" spans="2:2">
-      <c r="B333" s="3"/>
+      <c r="B333" s="4"/>
     </row>
     <row r="334" customHeight="1" spans="2:2">
-      <c r="B334" s="3"/>
+      <c r="B334" s="4"/>
     </row>
     <row r="335" customHeight="1" spans="2:2">
-      <c r="B335" s="3"/>
+      <c r="B335" s="4"/>
     </row>
     <row r="336" customHeight="1" spans="2:2">
-      <c r="B336" s="3"/>
+      <c r="B336" s="4"/>
     </row>
     <row r="337" customHeight="1" spans="2:2">
-      <c r="B337" s="3"/>
+      <c r="B337" s="4"/>
     </row>
     <row r="338" customHeight="1" spans="2:2">
-      <c r="B338" s="3"/>
+      <c r="B338" s="4"/>
     </row>
     <row r="339" customHeight="1" spans="2:2">
-      <c r="B339" s="3"/>
+      <c r="B339" s="4"/>
     </row>
     <row r="340" customHeight="1" spans="2:2">
-      <c r="B340" s="3"/>
+      <c r="B340" s="4"/>
     </row>
     <row r="341" customHeight="1" spans="2:2">
-      <c r="B341" s="3"/>
+      <c r="B341" s="4"/>
     </row>
     <row r="342" customHeight="1" spans="2:2">
-      <c r="B342" s="3"/>
+      <c r="B342" s="4"/>
     </row>
     <row r="343" customHeight="1" spans="2:2">
-      <c r="B343" s="3"/>
+      <c r="B343" s="4"/>
     </row>
     <row r="344" customHeight="1" spans="2:2">
-      <c r="B344" s="3"/>
+      <c r="B344" s="4"/>
     </row>
     <row r="345" customHeight="1" spans="2:2">
-      <c r="B345" s="3"/>
+      <c r="B345" s="4"/>
     </row>
     <row r="346" customHeight="1" spans="2:2">
-      <c r="B346" s="3"/>
+      <c r="B346" s="4"/>
     </row>
     <row r="347" customHeight="1" spans="2:2">
-      <c r="B347" s="3"/>
+      <c r="B347" s="4"/>
     </row>
     <row r="348" customHeight="1" spans="2:2">
-      <c r="B348" s="3"/>
+      <c r="B348" s="4"/>
     </row>
     <row r="349" customHeight="1" spans="2:2">
-      <c r="B349" s="3"/>
+      <c r="B349" s="4"/>
     </row>
     <row r="350" customHeight="1" spans="2:2">
-      <c r="B350" s="3"/>
+      <c r="B350" s="4"/>
     </row>
     <row r="351" customHeight="1" spans="2:2">
-      <c r="B351" s="3"/>
+      <c r="B351" s="4"/>
     </row>
     <row r="352" customHeight="1" spans="2:2">
-      <c r="B352" s="3"/>
+      <c r="B352" s="4"/>
     </row>
     <row r="353" customHeight="1" spans="2:2">
-      <c r="B353" s="3"/>
+      <c r="B353" s="4"/>
     </row>
     <row r="354" customHeight="1" spans="2:2">
-      <c r="B354" s="3"/>
+      <c r="B354" s="4"/>
     </row>
     <row r="355" customHeight="1" spans="2:2">
-      <c r="B355" s="3"/>
+      <c r="B355" s="4"/>
     </row>
     <row r="356" customHeight="1" spans="2:2">
-      <c r="B356" s="3"/>
+      <c r="B356" s="4"/>
     </row>
     <row r="357" customHeight="1" spans="2:2">
-      <c r="B357" s="3"/>
+      <c r="B357" s="4"/>
     </row>
     <row r="358" customHeight="1" spans="2:2">
-      <c r="B358" s="3"/>
+      <c r="B358" s="4"/>
     </row>
     <row r="359" customHeight="1" spans="2:2">
-      <c r="B359" s="3"/>
+      <c r="B359" s="4"/>
     </row>
     <row r="360" customHeight="1" spans="2:2">
-      <c r="B360" s="3"/>
+      <c r="B360" s="4"/>
     </row>
     <row r="361" customHeight="1" spans="2:2">
-      <c r="B361" s="3"/>
+      <c r="B361" s="4"/>
     </row>
     <row r="362" customHeight="1" spans="2:2">
-      <c r="B362" s="3"/>
+      <c r="B362" s="4"/>
     </row>
     <row r="363" customHeight="1" spans="2:2">
-      <c r="B363" s="3"/>
+      <c r="B363" s="4"/>
     </row>
     <row r="364" customHeight="1" spans="2:2">
-      <c r="B364" s="3"/>
+      <c r="B364" s="4"/>
     </row>
     <row r="365" customHeight="1" spans="2:2">
-      <c r="B365" s="3"/>
+      <c r="B365" s="4"/>
     </row>
     <row r="366" customHeight="1" spans="2:2">
-      <c r="B366" s="3"/>
+      <c r="B366" s="4"/>
     </row>
     <row r="367" customHeight="1" spans="2:2">
-      <c r="B367" s="3"/>
+      <c r="B367" s="4"/>
     </row>
     <row r="368" customHeight="1" spans="2:2">
-      <c r="B368" s="3"/>
+      <c r="B368" s="4"/>
     </row>
     <row r="369" customHeight="1" spans="2:2">
-      <c r="B369" s="3"/>
+      <c r="B369" s="4"/>
     </row>
     <row r="370" customHeight="1" spans="2:2">
-      <c r="B370" s="3"/>
+      <c r="B370" s="4"/>
     </row>
     <row r="371" customHeight="1" spans="2:2">
-      <c r="B371" s="3"/>
+      <c r="B371" s="4"/>
     </row>
     <row r="372" customHeight="1" spans="2:2">
-      <c r="B372" s="3"/>
+      <c r="B372" s="4"/>
     </row>
     <row r="373" customHeight="1" spans="2:2">
-      <c r="B373" s="3"/>
+      <c r="B373" s="4"/>
     </row>
     <row r="374" customHeight="1" spans="2:2">
-      <c r="B374" s="3"/>
+      <c r="B374" s="4"/>
     </row>
     <row r="375" customHeight="1" spans="2:2">
-      <c r="B375" s="3"/>
+      <c r="B375" s="4"/>
     </row>
     <row r="376" customHeight="1" spans="2:2">
-      <c r="B376" s="3"/>
+      <c r="B376" s="4"/>
     </row>
     <row r="377" customHeight="1" spans="2:2">
-      <c r="B377" s="3"/>
+      <c r="B377" s="4"/>
     </row>
     <row r="378" customHeight="1" spans="2:2">
-      <c r="B378" s="3"/>
+      <c r="B378" s="4"/>
     </row>
     <row r="379" customHeight="1" spans="2:2">
-      <c r="B379" s="3"/>
+      <c r="B379" s="4"/>
     </row>
     <row r="380" customHeight="1" spans="2:2">
-      <c r="B380" s="3"/>
+      <c r="B380" s="4"/>
     </row>
     <row r="381" customHeight="1" spans="2:2">
-      <c r="B381" s="3"/>
+      <c r="B381" s="4"/>
     </row>
     <row r="382" customHeight="1" spans="2:2">
-      <c r="B382" s="3"/>
+      <c r="B382" s="4"/>
     </row>
     <row r="383" customHeight="1" spans="2:2">
-      <c r="B383" s="3"/>
+      <c r="B383" s="4"/>
     </row>
     <row r="384" customHeight="1" spans="2:2">
-      <c r="B384" s="3"/>
+      <c r="B384" s="4"/>
     </row>
     <row r="385" customHeight="1" spans="2:2">
-      <c r="B385" s="3"/>
+      <c r="B385" s="4"/>
     </row>
     <row r="386" customHeight="1" spans="2:2">
-      <c r="B386" s="3"/>
+      <c r="B386" s="4"/>
     </row>
     <row r="387" customHeight="1" spans="2:2">
-      <c r="B387" s="3"/>
+      <c r="B387" s="4"/>
     </row>
     <row r="388" customHeight="1" spans="2:2">
-      <c r="B388" s="3"/>
+      <c r="B388" s="4"/>
     </row>
     <row r="389" customHeight="1" spans="2:2">
-      <c r="B389" s="3"/>
+      <c r="B389" s="4"/>
     </row>
     <row r="390" customHeight="1" spans="2:2">
-      <c r="B390" s="3"/>
+      <c r="B390" s="4"/>
     </row>
     <row r="391" customHeight="1" spans="2:2">
-      <c r="B391" s="3"/>
+      <c r="B391" s="4"/>
     </row>
     <row r="392" customHeight="1" spans="2:2">
-      <c r="B392" s="3"/>
+      <c r="B392" s="4"/>
     </row>
     <row r="393" customHeight="1" spans="2:2">
-      <c r="B393" s="3"/>
+      <c r="B393" s="4"/>
     </row>
     <row r="394" customHeight="1" spans="2:2">
-      <c r="B394" s="3"/>
+      <c r="B394" s="4"/>
     </row>
     <row r="395" customHeight="1" spans="2:2">
-      <c r="B395" s="3"/>
+      <c r="B395" s="4"/>
     </row>
     <row r="396" customHeight="1" spans="2:2">
-      <c r="B396" s="3"/>
+      <c r="B396" s="4"/>
     </row>
     <row r="397" customHeight="1" spans="2:2">
-      <c r="B397" s="3"/>
+      <c r="B397" s="4"/>
     </row>
     <row r="398" customHeight="1" spans="2:2">
-      <c r="B398" s="3"/>
+      <c r="B398" s="4"/>
     </row>
     <row r="399" customHeight="1" spans="2:2">
-      <c r="B399" s="3"/>
+      <c r="B399" s="4"/>
     </row>
     <row r="400" customHeight="1" spans="2:2">
-      <c r="B400" s="3"/>
+      <c r="B400" s="4"/>
     </row>
     <row r="401" customHeight="1" spans="2:2">
-      <c r="B401" s="3"/>
+      <c r="B401" s="4"/>
     </row>
     <row r="402" customHeight="1" spans="2:2">
-      <c r="B402" s="3"/>
+      <c r="B402" s="4"/>
     </row>
     <row r="403" customHeight="1" spans="2:2">
-      <c r="B403" s="3"/>
+      <c r="B403" s="4"/>
     </row>
     <row r="404" customHeight="1" spans="2:2">
-      <c r="B404" s="3"/>
+      <c r="B404" s="4"/>
     </row>
     <row r="405" customHeight="1" spans="2:2">
-      <c r="B405" s="3"/>
+      <c r="B405" s="4"/>
     </row>
     <row r="406" customHeight="1" spans="2:2">
-      <c r="B406" s="3"/>
+      <c r="B406" s="4"/>
     </row>
     <row r="407" customHeight="1" spans="2:2">
-      <c r="B407" s="3"/>
+      <c r="B407" s="4"/>
     </row>
     <row r="408" customHeight="1" spans="2:2">
-      <c r="B408" s="3"/>
+      <c r="B408" s="4"/>
     </row>
     <row r="409" customHeight="1" spans="2:2">
-      <c r="B409" s="3"/>
+      <c r="B409" s="4"/>
     </row>
     <row r="410" customHeight="1" spans="2:2">
-      <c r="B410" s="3"/>
+      <c r="B410" s="4"/>
     </row>
     <row r="411" customHeight="1" spans="2:2">
-      <c r="B411" s="3"/>
+      <c r="B411" s="4"/>
     </row>
     <row r="412" customHeight="1" spans="2:2">
-      <c r="B412" s="3"/>
+      <c r="B412" s="4"/>
     </row>
     <row r="413" customHeight="1" spans="2:2">
-      <c r="B413" s="3"/>
+      <c r="B413" s="4"/>
     </row>
     <row r="414" customHeight="1" spans="2:2">
-      <c r="B414" s="3"/>
+      <c r="B414" s="4"/>
     </row>
     <row r="415" customHeight="1" spans="2:2">
-      <c r="B415" s="3"/>
+      <c r="B415" s="4"/>
     </row>
     <row r="416" customHeight="1" spans="2:2">
-      <c r="B416" s="3"/>
+      <c r="B416" s="4"/>
     </row>
     <row r="417" customHeight="1" spans="2:2">
-      <c r="B417" s="3"/>
+      <c r="B417" s="4"/>
     </row>
     <row r="418" customHeight="1" spans="2:2">
-      <c r="B418" s="3"/>
+      <c r="B418" s="4"/>
     </row>
     <row r="419" customHeight="1" spans="2:2">
-      <c r="B419" s="3"/>
+      <c r="B419" s="4"/>
     </row>
     <row r="420" customHeight="1" spans="2:2">
-      <c r="B420" s="3"/>
+      <c r="B420" s="4"/>
     </row>
     <row r="421" customHeight="1" spans="2:2">
-      <c r="B421" s="3"/>
+      <c r="B421" s="4"/>
     </row>
     <row r="422" customHeight="1" spans="2:2">
-      <c r="B422" s="3"/>
+      <c r="B422" s="4"/>
     </row>
     <row r="423" customHeight="1" spans="2:2">
-      <c r="B423" s="3"/>
+      <c r="B423" s="4"/>
     </row>
     <row r="424" customHeight="1" spans="2:2">
-      <c r="B424" s="3"/>
+      <c r="B424" s="4"/>
     </row>
     <row r="425" customHeight="1" spans="2:2">
-      <c r="B425" s="3"/>
+      <c r="B425" s="4"/>
     </row>
     <row r="426" customHeight="1" spans="2:2">
-      <c r="B426" s="3"/>
+      <c r="B426" s="4"/>
     </row>
     <row r="427" customHeight="1" spans="2:2">
-      <c r="B427" s="3"/>
+      <c r="B427" s="4"/>
     </row>
     <row r="428" customHeight="1" spans="2:2">
-      <c r="B428" s="3"/>
+      <c r="B428" s="4"/>
     </row>
     <row r="429" customHeight="1" spans="2:2">
-      <c r="B429" s="3"/>
+      <c r="B429" s="4"/>
     </row>
     <row r="430" customHeight="1" spans="2:2">
-      <c r="B430" s="3"/>
+      <c r="B430" s="4"/>
     </row>
     <row r="431" customHeight="1" spans="2:2">
-      <c r="B431" s="3"/>
+      <c r="B431" s="4"/>
     </row>
     <row r="432" customHeight="1" spans="2:2">
-      <c r="B432" s="3"/>
+      <c r="B432" s="4"/>
     </row>
     <row r="433" customHeight="1" spans="2:2">
-      <c r="B433" s="3"/>
+      <c r="B433" s="4"/>
     </row>
     <row r="434" customHeight="1" spans="2:2">
-      <c r="B434" s="3"/>
+      <c r="B434" s="4"/>
     </row>
     <row r="435" customHeight="1" spans="2:2">
-      <c r="B435" s="3"/>
+      <c r="B435" s="4"/>
     </row>
     <row r="436" customHeight="1" spans="2:2">
-      <c r="B436" s="3"/>
+      <c r="B436" s="4"/>
     </row>
     <row r="437" customHeight="1" spans="2:2">
-      <c r="B437" s="3"/>
+      <c r="B437" s="4"/>
     </row>
     <row r="438" customHeight="1" spans="2:2">
-      <c r="B438" s="3"/>
+      <c r="B438" s="4"/>
     </row>
     <row r="439" customHeight="1" spans="2:2">
-      <c r="B439" s="3"/>
+      <c r="B439" s="4"/>
     </row>
     <row r="440" customHeight="1" spans="2:2">
-      <c r="B440" s="3"/>
+      <c r="B440" s="4"/>
     </row>
     <row r="441" customHeight="1" spans="2:2">
-      <c r="B441" s="3"/>
+      <c r="B441" s="4"/>
     </row>
     <row r="442" customHeight="1" spans="2:2">
-      <c r="B442" s="3"/>
+      <c r="B442" s="4"/>
     </row>
     <row r="443" customHeight="1" spans="2:2">
-      <c r="B443" s="3"/>
+      <c r="B443" s="4"/>
     </row>
     <row r="444" customHeight="1" spans="2:2">
-      <c r="B444" s="3"/>
+      <c r="B444" s="4"/>
     </row>
     <row r="445" customHeight="1" spans="2:2">
-      <c r="B445" s="3"/>
+      <c r="B445" s="4"/>
     </row>
     <row r="446" customHeight="1" spans="2:2">
-      <c r="B446" s="3"/>
+      <c r="B446" s="4"/>
     </row>
     <row r="447" customHeight="1" spans="2:2">
-      <c r="B447" s="3"/>
+      <c r="B447" s="4"/>
     </row>
     <row r="448" customHeight="1" spans="2:2">
-      <c r="B448" s="3"/>
+      <c r="B448" s="4"/>
     </row>
     <row r="449" customHeight="1" spans="2:2">
-      <c r="B449" s="3"/>
+      <c r="B449" s="4"/>
     </row>
     <row r="450" customHeight="1" spans="2:2">
-      <c r="B450" s="3"/>
+      <c r="B450" s="4"/>
     </row>
     <row r="451" customHeight="1" spans="2:2">
-      <c r="B451" s="3"/>
+      <c r="B451" s="4"/>
     </row>
     <row r="452" customHeight="1" spans="2:2">
-      <c r="B452" s="3"/>
+      <c r="B452" s="4"/>
     </row>
     <row r="453" customHeight="1" spans="2:2">
-      <c r="B453" s="3"/>
+      <c r="B453" s="4"/>
     </row>
     <row r="454" customHeight="1" spans="2:2">
-      <c r="B454" s="3"/>
+      <c r="B454" s="4"/>
     </row>
     <row r="455" customHeight="1" spans="2:2">
-      <c r="B455" s="3"/>
+      <c r="B455" s="4"/>
     </row>
     <row r="456" customHeight="1" spans="2:2">
-      <c r="B456" s="3"/>
+      <c r="B456" s="4"/>
     </row>
     <row r="457" customHeight="1" spans="2:2">
-      <c r="B457" s="3"/>
+      <c r="B457" s="4"/>
     </row>
     <row r="458" customHeight="1" spans="2:2">
-      <c r="B458" s="3"/>
+      <c r="B458" s="4"/>
     </row>
     <row r="459" customHeight="1" spans="2:2">
-      <c r="B459" s="3"/>
+      <c r="B459" s="4"/>
     </row>
     <row r="460" customHeight="1" spans="2:2">
-      <c r="B460" s="3"/>
+      <c r="B460" s="4"/>
     </row>
     <row r="461" customHeight="1" spans="2:2">
-      <c r="B461" s="3"/>
+      <c r="B461" s="4"/>
     </row>
     <row r="462" customHeight="1" spans="2:2">
-      <c r="B462" s="3"/>
+      <c r="B462" s="4"/>
     </row>
     <row r="463" customHeight="1" spans="2:2">
-      <c r="B463" s="3"/>
+      <c r="B463" s="4"/>
     </row>
     <row r="464" customHeight="1" spans="2:2">
-      <c r="B464" s="3"/>
+      <c r="B464" s="4"/>
     </row>
     <row r="465" customHeight="1" spans="2:2">
-      <c r="B465" s="3"/>
+      <c r="B465" s="4"/>
     </row>
     <row r="466" customHeight="1" spans="2:2">
-      <c r="B466" s="3"/>
+      <c r="B466" s="4"/>
     </row>
     <row r="467" customHeight="1" spans="2:2">
-      <c r="B467" s="3"/>
+      <c r="B467" s="4"/>
     </row>
     <row r="468" customHeight="1" spans="2:2">
-      <c r="B468" s="3"/>
+      <c r="B468" s="4"/>
     </row>
     <row r="469" customHeight="1" spans="2:2">
-      <c r="B469" s="3"/>
+      <c r="B469" s="4"/>
     </row>
     <row r="470" customHeight="1" spans="2:2">
-      <c r="B470" s="3"/>
+      <c r="B470" s="4"/>
     </row>
     <row r="471" customHeight="1" spans="2:2">
-      <c r="B471" s="3"/>
+      <c r="B471" s="4"/>
     </row>
     <row r="472" customHeight="1" spans="2:2">
-      <c r="B472" s="3"/>
+      <c r="B472" s="4"/>
     </row>
     <row r="473" customHeight="1" spans="2:2">
-      <c r="B473" s="3"/>
+      <c r="B473" s="4"/>
     </row>
     <row r="474" customHeight="1" spans="2:2">
-      <c r="B474" s="3"/>
+      <c r="B474" s="4"/>
     </row>
     <row r="475" customHeight="1" spans="2:2">
-      <c r="B475" s="3"/>
+      <c r="B475" s="4"/>
     </row>
     <row r="476" customHeight="1" spans="2:2">
-      <c r="B476" s="3"/>
+      <c r="B476" s="4"/>
     </row>
     <row r="477" customHeight="1" spans="2:2">
-      <c r="B477" s="3"/>
+      <c r="B477" s="4"/>
     </row>
     <row r="478" customHeight="1" spans="2:2">
-      <c r="B478" s="3"/>
+      <c r="B478" s="4"/>
     </row>
     <row r="479" customHeight="1" spans="2:2">
-      <c r="B479" s="3"/>
+      <c r="B479" s="4"/>
     </row>
     <row r="480" customHeight="1" spans="2:2">
-      <c r="B480" s="3"/>
+      <c r="B480" s="4"/>
     </row>
     <row r="481" customHeight="1" spans="2:2">
-      <c r="B481" s="3"/>
+      <c r="B481" s="4"/>
     </row>
     <row r="482" customHeight="1" spans="2:2">
-      <c r="B482" s="3"/>
+      <c r="B482" s="4"/>
     </row>
     <row r="483" customHeight="1" spans="2:2">
-      <c r="B483" s="3"/>
+      <c r="B483" s="4"/>
     </row>
     <row r="484" customHeight="1" spans="2:2">
-      <c r="B484" s="3"/>
+      <c r="B484" s="4"/>
     </row>
     <row r="485" customHeight="1" spans="2:2">
-      <c r="B485" s="3"/>
+      <c r="B485" s="4"/>
     </row>
     <row r="486" customHeight="1" spans="2:2">
-      <c r="B486" s="3"/>
+      <c r="B486" s="4"/>
     </row>
     <row r="487" customHeight="1" spans="2:2">
-      <c r="B487" s="3"/>
+      <c r="B487" s="4"/>
     </row>
     <row r="488" customHeight="1" spans="2:2">
-      <c r="B488" s="3"/>
+      <c r="B488" s="4"/>
     </row>
     <row r="489" customHeight="1" spans="2:2">
-      <c r="B489" s="3"/>
+      <c r="B489" s="4"/>
     </row>
     <row r="490" customHeight="1" spans="2:2">
-      <c r="B490" s="3"/>
+      <c r="B490" s="4"/>
     </row>
     <row r="491" customHeight="1" spans="2:2">
-      <c r="B491" s="3"/>
+      <c r="B491" s="4"/>
     </row>
     <row r="492" customHeight="1" spans="2:2">
-      <c r="B492" s="3"/>
+      <c r="B492" s="4"/>
     </row>
     <row r="493" customHeight="1" spans="2:2">
-      <c r="B493" s="3"/>
+      <c r="B493" s="4"/>
     </row>
     <row r="494" customHeight="1" spans="2:2">
-      <c r="B494" s="3"/>
+      <c r="B494" s="4"/>
     </row>
     <row r="495" customHeight="1" spans="2:2">
-      <c r="B495" s="3"/>
+      <c r="B495" s="4"/>
     </row>
     <row r="496" customHeight="1" spans="2:2">
-      <c r="B496" s="3"/>
+      <c r="B496" s="4"/>
     </row>
     <row r="497" customHeight="1" spans="2:2">
-      <c r="B497" s="3"/>
+      <c r="B497" s="4"/>
     </row>
     <row r="498" customHeight="1" spans="2:2">
-      <c r="B498" s="3"/>
+      <c r="B498" s="4"/>
     </row>
     <row r="499" customHeight="1" spans="2:2">
-      <c r="B499" s="3"/>
+      <c r="B499" s="4"/>
     </row>
     <row r="500" customHeight="1" spans="2:2">
-      <c r="B500" s="3"/>
+      <c r="B500" s="4"/>
     </row>
     <row r="501" customHeight="1" spans="2:2">
-      <c r="B501" s="3"/>
+      <c r="B501" s="4"/>
     </row>
     <row r="502" customHeight="1" spans="2:2">
-      <c r="B502" s="3"/>
+      <c r="B502" s="4"/>
     </row>
     <row r="503" customHeight="1" spans="2:2">
-      <c r="B503" s="3"/>
+      <c r="B503" s="4"/>
     </row>
     <row r="504" customHeight="1" spans="2:2">
-      <c r="B504" s="3"/>
+      <c r="B504" s="4"/>
     </row>
     <row r="505" customHeight="1" spans="2:2">
-      <c r="B505" s="3"/>
+      <c r="B505" s="4"/>
     </row>
     <row r="506" customHeight="1" spans="2:2">
-      <c r="B506" s="3"/>
+      <c r="B506" s="4"/>
     </row>
     <row r="507" customHeight="1" spans="2:2">
-      <c r="B507" s="3"/>
+      <c r="B507" s="4"/>
     </row>
     <row r="508" customHeight="1" spans="2:2">
-      <c r="B508" s="3"/>
+      <c r="B508" s="4"/>
     </row>
     <row r="509" customHeight="1" spans="2:2">
-      <c r="B509" s="3"/>
+      <c r="B509" s="4"/>
     </row>
     <row r="510" customHeight="1" spans="2:2">
-      <c r="B510" s="3"/>
+      <c r="B510" s="4"/>
     </row>
     <row r="511" customHeight="1" spans="2:2">
-      <c r="B511" s="3"/>
+      <c r="B511" s="4"/>
     </row>
     <row r="512" customHeight="1" spans="2:2">
-      <c r="B512" s="3"/>
+      <c r="B512" s="4"/>
     </row>
     <row r="513" customHeight="1" spans="2:2">
-      <c r="B513" s="3"/>
+      <c r="B513" s="4"/>
     </row>
     <row r="514" customHeight="1" spans="2:2">
-      <c r="B514" s="3"/>
+      <c r="B514" s="4"/>
     </row>
     <row r="515" customHeight="1" spans="2:2">
-      <c r="B515" s="3"/>
+      <c r="B515" s="4"/>
     </row>
     <row r="516" customHeight="1" spans="2:2">
-      <c r="B516" s="3"/>
+      <c r="B516" s="4"/>
     </row>
     <row r="517" customHeight="1" spans="2:2">
-      <c r="B517" s="3"/>
+      <c r="B517" s="4"/>
     </row>
     <row r="518" customHeight="1" spans="2:2">
-      <c r="B518" s="3"/>
+      <c r="B518" s="4"/>
     </row>
     <row r="519" customHeight="1" spans="2:2">
-      <c r="B519" s="3"/>
+      <c r="B519" s="4"/>
     </row>
     <row r="520" customHeight="1" spans="2:2">
-      <c r="B520" s="3"/>
+      <c r="B520" s="4"/>
     </row>
     <row r="521" customHeight="1" spans="2:2">
-      <c r="B521" s="3"/>
+      <c r="B521" s="4"/>
     </row>
     <row r="522" customHeight="1" spans="2:2">
-      <c r="B522" s="3"/>
+      <c r="B522" s="4"/>
     </row>
     <row r="523" customHeight="1" spans="2:2">
-      <c r="B523" s="3"/>
+      <c r="B523" s="4"/>
     </row>
     <row r="524" customHeight="1" spans="2:2">
-      <c r="B524" s="3"/>
+      <c r="B524" s="4"/>
     </row>
     <row r="525" customHeight="1" spans="2:2">
-      <c r="B525" s="3"/>
+      <c r="B525" s="4"/>
     </row>
     <row r="526" customHeight="1" spans="2:2">
-      <c r="B526" s="3"/>
+      <c r="B526" s="4"/>
     </row>
     <row r="527" customHeight="1" spans="2:2">
-      <c r="B527" s="3"/>
+      <c r="B527" s="4"/>
     </row>
     <row r="528" customHeight="1" spans="2:2">
-      <c r="B528" s="3"/>
+      <c r="B528" s="4"/>
     </row>
     <row r="529" customHeight="1" spans="2:2">
-      <c r="B529" s="3"/>
+      <c r="B529" s="4"/>
     </row>
     <row r="530" customHeight="1" spans="2:2">
-      <c r="B530" s="3"/>
+      <c r="B530" s="4"/>
     </row>
     <row r="531" customHeight="1" spans="2:2">
-      <c r="B531" s="3"/>
+      <c r="B531" s="4"/>
     </row>
     <row r="532" customHeight="1" spans="2:2">
-      <c r="B532" s="3"/>
+      <c r="B532" s="4"/>
     </row>
     <row r="533" customHeight="1" spans="2:2">
-      <c r="B533" s="3"/>
+      <c r="B533" s="4"/>
     </row>
     <row r="534" customHeight="1" spans="2:2">
-      <c r="B534" s="3"/>
+      <c r="B534" s="4"/>
     </row>
     <row r="535" customHeight="1" spans="2:2">
-      <c r="B535" s="3"/>
+      <c r="B535" s="4"/>
     </row>
     <row r="536" customHeight="1" spans="2:2">
-      <c r="B536" s="3"/>
+      <c r="B536" s="4"/>
     </row>
     <row r="537" customHeight="1" spans="2:2">
-      <c r="B537" s="3"/>
+      <c r="B537" s="4"/>
     </row>
     <row r="538" customHeight="1" spans="2:2">
-      <c r="B538" s="3"/>
+      <c r="B538" s="4"/>
     </row>
     <row r="539" customHeight="1" spans="2:2">
-      <c r="B539" s="3"/>
+      <c r="B539" s="4"/>
     </row>
     <row r="540" customHeight="1" spans="2:2">
-      <c r="B540" s="3"/>
+      <c r="B540" s="4"/>
     </row>
     <row r="541" customHeight="1" spans="2:2">
-      <c r="B541" s="3"/>
+      <c r="B541" s="4"/>
     </row>
     <row r="542" customHeight="1" spans="2:2">
-      <c r="B542" s="3"/>
+      <c r="B542" s="4"/>
     </row>
     <row r="543" customHeight="1" spans="2:2">
-      <c r="B543" s="3"/>
+      <c r="B543" s="4"/>
     </row>
     <row r="544" customHeight="1" spans="2:2">
-      <c r="B544" s="3"/>
+      <c r="B544" s="4"/>
     </row>
     <row r="545" customHeight="1" spans="2:2">
-      <c r="B545" s="3"/>
+      <c r="B545" s="4"/>
     </row>
     <row r="546" customHeight="1" spans="2:2">
-      <c r="B546" s="3"/>
+      <c r="B546" s="4"/>
     </row>
     <row r="547" customHeight="1" spans="2:2">
-      <c r="B547" s="3"/>
+      <c r="B547" s="4"/>
     </row>
     <row r="548" customHeight="1" spans="2:2">
-      <c r="B548" s="3"/>
+      <c r="B548" s="4"/>
     </row>
     <row r="549" customHeight="1" spans="2:2">
-      <c r="B549" s="3"/>
+      <c r="B549" s="4"/>
     </row>
     <row r="550" customHeight="1" spans="2:2">
-      <c r="B550" s="3"/>
+      <c r="B550" s="4"/>
     </row>
     <row r="551" customHeight="1" spans="2:2">
-      <c r="B551" s="3"/>
+      <c r="B551" s="4"/>
     </row>
     <row r="552" customHeight="1" spans="2:2">
-      <c r="B552" s="3"/>
+      <c r="B552" s="4"/>
     </row>
     <row r="553" customHeight="1" spans="2:2">
-      <c r="B553" s="3"/>
+      <c r="B553" s="4"/>
     </row>
     <row r="554" customHeight="1" spans="2:2">
-      <c r="B554" s="3"/>
+      <c r="B554" s="4"/>
     </row>
     <row r="555" customHeight="1" spans="2:2">
-      <c r="B555" s="3"/>
+      <c r="B555" s="4"/>
     </row>
     <row r="556" customHeight="1" spans="2:2">
-      <c r="B556" s="3"/>
+      <c r="B556" s="4"/>
     </row>
     <row r="557" customHeight="1" spans="2:2">
-      <c r="B557" s="3"/>
+      <c r="B557" s="4"/>
     </row>
     <row r="558" customHeight="1" spans="2:2">
-      <c r="B558" s="3"/>
+      <c r="B558" s="4"/>
     </row>
     <row r="559" customHeight="1" spans="2:2">
-      <c r="B559" s="3"/>
+      <c r="B559" s="4"/>
     </row>
     <row r="560" customHeight="1" spans="2:2">
-      <c r="B560" s="3"/>
+      <c r="B560" s="4"/>
     </row>
     <row r="561" customHeight="1" spans="2:2">
-      <c r="B561" s="3"/>
+      <c r="B561" s="4"/>
     </row>
     <row r="562" customHeight="1" spans="2:2">
-      <c r="B562" s="3"/>
+      <c r="B562" s="4"/>
     </row>
     <row r="563" customHeight="1" spans="2:2">
-      <c r="B563" s="3"/>
+      <c r="B563" s="4"/>
     </row>
     <row r="564" customHeight="1" spans="2:2">
-      <c r="B564" s="3"/>
+      <c r="B564" s="4"/>
     </row>
     <row r="565" customHeight="1" spans="2:2">
-      <c r="B565" s="3"/>
+      <c r="B565" s="4"/>
     </row>
     <row r="566" customHeight="1" spans="2:2">
-      <c r="B566" s="3"/>
+      <c r="B566" s="4"/>
     </row>
     <row r="567" customHeight="1" spans="2:2">
-      <c r="B567" s="3"/>
+      <c r="B567" s="4"/>
     </row>
     <row r="568" customHeight="1" spans="2:2">
-      <c r="B568" s="3"/>
+      <c r="B568" s="4"/>
     </row>
     <row r="569" customHeight="1" spans="2:2">
-      <c r="B569" s="3"/>
+      <c r="B569" s="4"/>
     </row>
     <row r="570" customHeight="1" spans="2:2">
-      <c r="B570" s="3"/>
+      <c r="B570" s="4"/>
     </row>
     <row r="571" customHeight="1" spans="2:2">
-      <c r="B571" s="3"/>
+      <c r="B571" s="4"/>
     </row>
     <row r="572" customHeight="1" spans="2:2">
-      <c r="B572" s="3"/>
+      <c r="B572" s="4"/>
     </row>
     <row r="573" customHeight="1" spans="2:2">
-      <c r="B573" s="3"/>
+      <c r="B573" s="4"/>
     </row>
     <row r="574" customHeight="1" spans="2:2">
-      <c r="B574" s="3"/>
+      <c r="B574" s="4"/>
     </row>
     <row r="575" customHeight="1" spans="2:2">
-      <c r="B575" s="3"/>
+      <c r="B575" s="4"/>
     </row>
     <row r="576" customHeight="1" spans="2:2">
-      <c r="B576" s="3"/>
+      <c r="B576" s="4"/>
     </row>
     <row r="577" customHeight="1" spans="2:2">
-      <c r="B577" s="3"/>
+      <c r="B577" s="4"/>
     </row>
     <row r="578" customHeight="1" spans="2:2">
-      <c r="B578" s="3"/>
+      <c r="B578" s="4"/>
     </row>
     <row r="579" customHeight="1" spans="2:2">
-      <c r="B579" s="3"/>
+      <c r="B579" s="4"/>
     </row>
     <row r="580" customHeight="1" spans="2:2">
-      <c r="B580" s="3"/>
+      <c r="B580" s="4"/>
     </row>
     <row r="581" customHeight="1" spans="2:2">
-      <c r="B581" s="3"/>
+      <c r="B581" s="4"/>
     </row>
     <row r="582" customHeight="1" spans="2:2">
-      <c r="B582" s="3"/>
+      <c r="B582" s="4"/>
     </row>
     <row r="583" customHeight="1" spans="2:2">
-      <c r="B583" s="3"/>
+      <c r="B583" s="4"/>
     </row>
     <row r="584" customHeight="1" spans="2:2">
-      <c r="B584" s="3"/>
+      <c r="B584" s="4"/>
     </row>
     <row r="585" customHeight="1" spans="2:2">
-      <c r="B585" s="3"/>
+      <c r="B585" s="4"/>
     </row>
     <row r="586" customHeight="1" spans="2:2">
-      <c r="B586" s="3"/>
+      <c r="B586" s="4"/>
     </row>
     <row r="587" customHeight="1" spans="2:2">
-      <c r="B587" s="3"/>
+      <c r="B587" s="4"/>
     </row>
     <row r="588" customHeight="1" spans="2:2">
-      <c r="B588" s="3"/>
+      <c r="B588" s="4"/>
     </row>
     <row r="589" customHeight="1" spans="2:2">
-      <c r="B589" s="3"/>
+      <c r="B589" s="4"/>
     </row>
     <row r="590" customHeight="1" spans="2:2">
-      <c r="B590" s="3"/>
+      <c r="B590" s="4"/>
     </row>
     <row r="591" customHeight="1" spans="2:2">
-      <c r="B591" s="3"/>
+      <c r="B591" s="4"/>
     </row>
     <row r="592" customHeight="1" spans="2:2">
-      <c r="B592" s="3"/>
+      <c r="B592" s="4"/>
     </row>
     <row r="593" customHeight="1" spans="2:2">
-      <c r="B593" s="3"/>
+      <c r="B593" s="4"/>
     </row>
     <row r="594" customHeight="1" spans="2:2">
-      <c r="B594" s="3"/>
+      <c r="B594" s="4"/>
     </row>
     <row r="595" customHeight="1" spans="2:2">
-      <c r="B595" s="3"/>
+      <c r="B595" s="4"/>
     </row>
     <row r="596" customHeight="1" spans="2:2">
-      <c r="B596" s="3"/>
+      <c r="B596" s="4"/>
     </row>
     <row r="597" customHeight="1" spans="2:2">
-      <c r="B597" s="3"/>
+      <c r="B597" s="4"/>
     </row>
     <row r="598" customHeight="1" spans="2:2">
-      <c r="B598" s="3"/>
+      <c r="B598" s="4"/>
     </row>
     <row r="599" customHeight="1" spans="2:2">
-      <c r="B599" s="3"/>
+      <c r="B599" s="4"/>
     </row>
     <row r="600" customHeight="1" spans="2:2">
-      <c r="B600" s="3"/>
+      <c r="B600" s="4"/>
     </row>
     <row r="601" customHeight="1" spans="2:2">
-      <c r="B601" s="3"/>
+      <c r="B601" s="4"/>
     </row>
     <row r="602" customHeight="1" spans="2:2">
-      <c r="B602" s="3"/>
+      <c r="B602" s="4"/>
     </row>
     <row r="603" customHeight="1" spans="2:2">
-      <c r="B603" s="3"/>
+      <c r="B603" s="4"/>
     </row>
     <row r="604" customHeight="1" spans="2:2">
-      <c r="B604" s="3"/>
+      <c r="B604" s="4"/>
     </row>
     <row r="605" customHeight="1" spans="2:2">
-      <c r="B605" s="3"/>
+      <c r="B605" s="4"/>
     </row>
     <row r="606" customHeight="1" spans="2:2">
-      <c r="B606" s="3"/>
+      <c r="B606" s="4"/>
     </row>
     <row r="607" customHeight="1" spans="2:2">
-      <c r="B607" s="3"/>
+      <c r="B607" s="4"/>
     </row>
     <row r="608" customHeight="1" spans="2:2">
-      <c r="B608" s="3"/>
+      <c r="B608" s="4"/>
     </row>
     <row r="609" customHeight="1" spans="2:2">
-      <c r="B609" s="3"/>
+      <c r="B609" s="4"/>
     </row>
     <row r="610" customHeight="1" spans="2:2">
-      <c r="B610" s="3"/>
+      <c r="B610" s="4"/>
     </row>
     <row r="611" customHeight="1" spans="2:2">
-      <c r="B611" s="3"/>
+      <c r="B611" s="4"/>
     </row>
     <row r="612" customHeight="1" spans="2:2">
-      <c r="B612" s="3"/>
+      <c r="B612" s="4"/>
     </row>
     <row r="613" customHeight="1" spans="2:2">
-      <c r="B613" s="3"/>
+      <c r="B613" s="4"/>
     </row>
     <row r="614" customHeight="1" spans="2:2">
-      <c r="B614" s="3"/>
+      <c r="B614" s="4"/>
     </row>
     <row r="615" customHeight="1" spans="2:2">
-      <c r="B615" s="3"/>
+      <c r="B615" s="4"/>
     </row>
     <row r="616" customHeight="1" spans="2:2">
-      <c r="B616" s="3"/>
+      <c r="B616" s="4"/>
     </row>
     <row r="617" customHeight="1" spans="2:2">
-      <c r="B617" s="3"/>
+      <c r="B617" s="4"/>
     </row>
     <row r="618" customHeight="1" spans="2:2">
-      <c r="B618" s="3"/>
+      <c r="B618" s="4"/>
     </row>
     <row r="619" customHeight="1" spans="2:2">
-      <c r="B619" s="3"/>
+      <c r="B619" s="4"/>
     </row>
     <row r="620" customHeight="1" spans="2:2">
-      <c r="B620" s="3"/>
+      <c r="B620" s="4"/>
     </row>
     <row r="621" customHeight="1" spans="2:2">
-      <c r="B621" s="3"/>
+      <c r="B621" s="4"/>
     </row>
     <row r="622" customHeight="1" spans="2:2">
-      <c r="B622" s="3"/>
+      <c r="B622" s="4"/>
     </row>
     <row r="623" customHeight="1" spans="2:2">
-      <c r="B623" s="3"/>
+      <c r="B623" s="4"/>
     </row>
     <row r="624" customHeight="1" spans="2:2">
-      <c r="B624" s="3"/>
+      <c r="B624" s="4"/>
     </row>
     <row r="625" customHeight="1" spans="2:2">
-      <c r="B625" s="3"/>
+      <c r="B625" s="4"/>
     </row>
     <row r="626" customHeight="1" spans="2:2">
-      <c r="B626" s="3"/>
+      <c r="B626" s="4"/>
     </row>
     <row r="627" customHeight="1" spans="2:2">
-      <c r="B627" s="3"/>
+      <c r="B627" s="4"/>
     </row>
     <row r="628" customHeight="1" spans="2:2">
-      <c r="B628" s="3"/>
+      <c r="B628" s="4"/>
     </row>
     <row r="629" customHeight="1" spans="2:2">
-      <c r="B629" s="3"/>
+      <c r="B629" s="4"/>
     </row>
     <row r="630" customHeight="1" spans="2:2">
-      <c r="B630" s="3"/>
+      <c r="B630" s="4"/>
     </row>
     <row r="631" customHeight="1" spans="2:2">
-      <c r="B631" s="3"/>
+      <c r="B631" s="4"/>
     </row>
     <row r="632" customHeight="1" spans="2:2">
-      <c r="B632" s="3"/>
+      <c r="B632" s="4"/>
     </row>
     <row r="633" customHeight="1" spans="2:2">
-      <c r="B633" s="3"/>
+      <c r="B633" s="4"/>
     </row>
     <row r="634" customHeight="1" spans="2:2">
-      <c r="B634" s="3"/>
+      <c r="B634" s="4"/>
     </row>
     <row r="635" customHeight="1" spans="2:2">
-      <c r="B635" s="3"/>
+      <c r="B635" s="4"/>
     </row>
     <row r="636" customHeight="1" spans="2:2">
-      <c r="B636" s="3"/>
+      <c r="B636" s="4"/>
     </row>
     <row r="637" customHeight="1" spans="2:2">
-      <c r="B637" s="3"/>
+      <c r="B637" s="4"/>
     </row>
     <row r="638" customHeight="1" spans="2:2">
-      <c r="B638" s="3"/>
+      <c r="B638" s="4"/>
     </row>
     <row r="639" customHeight="1" spans="2:2">
-      <c r="B639" s="3"/>
+      <c r="B639" s="4"/>
     </row>
     <row r="640" customHeight="1" spans="2:2">
-      <c r="B640" s="3"/>
+      <c r="B640" s="4"/>
     </row>
     <row r="641" customHeight="1" spans="2:2">
-      <c r="B641" s="3"/>
+      <c r="B641" s="4"/>
     </row>
     <row r="642" customHeight="1" spans="2:2">
-      <c r="B642" s="3"/>
+      <c r="B642" s="4"/>
     </row>
     <row r="643" customHeight="1" spans="2:2">
-      <c r="B643" s="3"/>
+      <c r="B643" s="4"/>
     </row>
     <row r="644" customHeight="1" spans="2:2">
-      <c r="B644" s="3"/>
+      <c r="B644" s="4"/>
     </row>
     <row r="645" customHeight="1" spans="2:2">
-      <c r="B645" s="3"/>
+      <c r="B645" s="4"/>
     </row>
     <row r="646" customHeight="1" spans="2:2">
-      <c r="B646" s="3"/>
+      <c r="B646" s="4"/>
     </row>
     <row r="647" customHeight="1" spans="2:2">
-      <c r="B647" s="3"/>
+      <c r="B647" s="4"/>
     </row>
     <row r="648" customHeight="1" spans="2:2">
-      <c r="B648" s="3"/>
+      <c r="B648" s="4"/>
     </row>
     <row r="649" customHeight="1" spans="2:2">
-      <c r="B649" s="3"/>
+      <c r="B649" s="4"/>
     </row>
     <row r="650" customHeight="1" spans="2:2">
-      <c r="B650" s="3"/>
+      <c r="B650" s="4"/>
     </row>
     <row r="651" customHeight="1" spans="2:2">
-      <c r="B651" s="3"/>
+      <c r="B651" s="4"/>
     </row>
     <row r="652" customHeight="1" spans="2:2">
-      <c r="B652" s="3"/>
+      <c r="B652" s="4"/>
     </row>
     <row r="653" customHeight="1" spans="2:2">
-      <c r="B653" s="3"/>
+      <c r="B653" s="4"/>
     </row>
     <row r="654" customHeight="1" spans="2:2">
-      <c r="B654" s="3"/>
+      <c r="B654" s="4"/>
     </row>
     <row r="655" customHeight="1" spans="2:2">
-      <c r="B655" s="3"/>
+      <c r="B655" s="4"/>
     </row>
     <row r="656" customHeight="1" spans="2:2">
-      <c r="B656" s="3"/>
+      <c r="B656" s="4"/>
     </row>
     <row r="657" customHeight="1" spans="2:2">
-      <c r="B657" s="3"/>
+      <c r="B657" s="4"/>
     </row>
     <row r="658" customHeight="1" spans="2:2">
-      <c r="B658" s="3"/>
+      <c r="B658" s="4"/>
     </row>
     <row r="659" customHeight="1" spans="2:2">
-      <c r="B659" s="3"/>
+      <c r="B659" s="4"/>
     </row>
     <row r="660" customHeight="1" spans="2:2">
-      <c r="B660" s="3"/>
+      <c r="B660" s="4"/>
     </row>
     <row r="661" customHeight="1" spans="2:2">
-      <c r="B661" s="3"/>
+      <c r="B661" s="4"/>
     </row>
     <row r="662" customHeight="1" spans="2:2">
-      <c r="B662" s="3"/>
+      <c r="B662" s="4"/>
     </row>
     <row r="663" customHeight="1" spans="2:2">
-      <c r="B663" s="3"/>
+      <c r="B663" s="4"/>
     </row>
     <row r="664" customHeight="1" spans="2:2">
-      <c r="B664" s="3"/>
+      <c r="B664" s="4"/>
     </row>
     <row r="665" customHeight="1" spans="2:2">
-      <c r="B665" s="3"/>
+      <c r="B665" s="4"/>
     </row>
     <row r="666" customHeight="1" spans="2:2">
-      <c r="B666" s="3"/>
+      <c r="B666" s="4"/>
     </row>
     <row r="667" customHeight="1" spans="2:2">
-      <c r="B667" s="3"/>
+      <c r="B667" s="4"/>
     </row>
     <row r="668" customHeight="1" spans="2:2">
-      <c r="B668" s="3"/>
+      <c r="B668" s="4"/>
     </row>
     <row r="669" customHeight="1" spans="2:2">
-      <c r="B669" s="3"/>
+      <c r="B669" s="4"/>
     </row>
     <row r="670" customHeight="1" spans="2:2">
-      <c r="B670" s="3"/>
+      <c r="B670" s="4"/>
     </row>
     <row r="671" customHeight="1" spans="2:2">
-      <c r="B671" s="3"/>
+      <c r="B671" s="4"/>
     </row>
     <row r="672" customHeight="1" spans="2:2">
-      <c r="B672" s="3"/>
+      <c r="B672" s="4"/>
     </row>
     <row r="673" customHeight="1" spans="2:2">
-      <c r="B673" s="3"/>
+      <c r="B673" s="4"/>
     </row>
     <row r="674" customHeight="1" spans="2:2">
-      <c r="B674" s="3"/>
+      <c r="B674" s="4"/>
     </row>
     <row r="675" customHeight="1" spans="2:2">
-      <c r="B675" s="3"/>
+      <c r="B675" s="4"/>
     </row>
     <row r="676" customHeight="1" spans="2:2">
-      <c r="B676" s="3"/>
+      <c r="B676" s="4"/>
     </row>
     <row r="677" customHeight="1" spans="2:2">
-      <c r="B677" s="3"/>
+      <c r="B677" s="4"/>
     </row>
     <row r="678" customHeight="1" spans="2:2">
-      <c r="B678" s="3"/>
+      <c r="B678" s="4"/>
     </row>
     <row r="679" customHeight="1" spans="2:2">
-      <c r="B679" s="3"/>
+      <c r="B679" s="4"/>
     </row>
     <row r="680" customHeight="1" spans="2:2">
-      <c r="B680" s="3"/>
+      <c r="B680" s="4"/>
     </row>
     <row r="681" customHeight="1" spans="2:2">
-      <c r="B681" s="3"/>
+      <c r="B681" s="4"/>
     </row>
     <row r="682" customHeight="1" spans="2:2">
-      <c r="B682" s="3"/>
+      <c r="B682" s="4"/>
     </row>
     <row r="683" customHeight="1" spans="2:2">
-      <c r="B683" s="3"/>
+      <c r="B683" s="4"/>
     </row>
     <row r="684" customHeight="1" spans="2:2">
-      <c r="B684" s="3"/>
+      <c r="B684" s="4"/>
     </row>
     <row r="685" customHeight="1" spans="2:2">
-      <c r="B685" s="3"/>
+      <c r="B685" s="4"/>
     </row>
     <row r="686" customHeight="1" spans="2:2">
-      <c r="B686" s="3"/>
+      <c r="B686" s="4"/>
     </row>
     <row r="687" customHeight="1" spans="2:2">
-      <c r="B687" s="3"/>
+      <c r="B687" s="4"/>
     </row>
     <row r="688" customHeight="1" spans="2:2">
-      <c r="B688" s="3"/>
+      <c r="B688" s="4"/>
     </row>
     <row r="689" customHeight="1" spans="2:2">
-      <c r="B689" s="3"/>
+      <c r="B689" s="4"/>
     </row>
     <row r="690" customHeight="1" spans="2:2">
-      <c r="B690" s="3"/>
+      <c r="B690" s="4"/>
     </row>
     <row r="691" customHeight="1" spans="2:2">
-      <c r="B691" s="3"/>
+      <c r="B691" s="4"/>
     </row>
     <row r="692" customHeight="1" spans="2:2">
-      <c r="B692" s="3"/>
+      <c r="B692" s="4"/>
     </row>
     <row r="693" customHeight="1" spans="2:2">
-      <c r="B693" s="3"/>
+      <c r="B693" s="4"/>
     </row>
     <row r="694" customHeight="1" spans="2:2">
-      <c r="B694" s="3"/>
+      <c r="B694" s="4"/>
     </row>
     <row r="695" customHeight="1" spans="2:2">
-      <c r="B695" s="3"/>
+      <c r="B695" s="4"/>
     </row>
     <row r="696" customHeight="1" spans="2:2">
-      <c r="B696" s="3"/>
+      <c r="B696" s="4"/>
     </row>
     <row r="697" customHeight="1" spans="2:2">
-      <c r="B697" s="3"/>
+      <c r="B697" s="4"/>
     </row>
     <row r="698" customHeight="1" spans="2:2">
-      <c r="B698" s="3"/>
+      <c r="B698" s="4"/>
     </row>
     <row r="699" customHeight="1" spans="2:2">
-      <c r="B699" s="3"/>
+      <c r="B699" s="4"/>
     </row>
     <row r="700" customHeight="1" spans="2:2">
-      <c r="B700" s="3"/>
+      <c r="B700" s="4"/>
     </row>
     <row r="701" customHeight="1" spans="2:2">
-      <c r="B701" s="3"/>
+      <c r="B701" s="4"/>
     </row>
     <row r="702" customHeight="1" spans="2:2">
-      <c r="B702" s="3"/>
+      <c r="B702" s="4"/>
     </row>
     <row r="703" customHeight="1" spans="2:2">
-      <c r="B703" s="3"/>
+      <c r="B703" s="4"/>
     </row>
     <row r="704" customHeight="1" spans="2:2">
-      <c r="B704" s="3"/>
+      <c r="B704" s="4"/>
     </row>
     <row r="705" customHeight="1" spans="2:2">
-      <c r="B705" s="3"/>
+      <c r="B705" s="4"/>
     </row>
     <row r="706" customHeight="1" spans="2:2">
-      <c r="B706" s="3"/>
+      <c r="B706" s="4"/>
     </row>
     <row r="707" customHeight="1" spans="2:2">
-      <c r="B707" s="3"/>
+      <c r="B707" s="4"/>
     </row>
     <row r="708" customHeight="1" spans="2:2">
-      <c r="B708" s="3"/>
+      <c r="B708" s="4"/>
     </row>
     <row r="709" customHeight="1" spans="2:2">
-      <c r="B709" s="3"/>
+      <c r="B709" s="4"/>
     </row>
     <row r="710" customHeight="1" spans="2:2">
-      <c r="B710" s="3"/>
+      <c r="B710" s="4"/>
     </row>
     <row r="711" customHeight="1" spans="2:2">
-      <c r="B711" s="3"/>
+      <c r="B711" s="4"/>
     </row>
     <row r="712" customHeight="1" spans="2:2">
-      <c r="B712" s="3"/>
+      <c r="B712" s="4"/>
     </row>
     <row r="713" customHeight="1" spans="2:2">
-      <c r="B713" s="3"/>
+      <c r="B713" s="4"/>
     </row>
     <row r="714" customHeight="1" spans="2:2">
-      <c r="B714" s="3"/>
+      <c r="B714" s="4"/>
     </row>
     <row r="715" customHeight="1" spans="2:2">
-      <c r="B715" s="3"/>
+      <c r="B715" s="4"/>
     </row>
     <row r="716" customHeight="1" spans="2:2">
-      <c r="B716" s="3"/>
+      <c r="B716" s="4"/>
     </row>
     <row r="717" customHeight="1" spans="2:2">
-      <c r="B717" s="3"/>
+      <c r="B717" s="4"/>
     </row>
     <row r="718" customHeight="1" spans="2:2">
-      <c r="B718" s="3"/>
+      <c r="B718" s="4"/>
     </row>
     <row r="719" customHeight="1" spans="2:2">
-      <c r="B719" s="3"/>
+      <c r="B719" s="4"/>
     </row>
     <row r="720" customHeight="1" spans="2:2">
-      <c r="B720" s="3"/>
+      <c r="B720" s="4"/>
     </row>
     <row r="721" customHeight="1" spans="2:2">
-      <c r="B721" s="3"/>
+      <c r="B721" s="4"/>
     </row>
     <row r="722" customHeight="1" spans="2:2">
-      <c r="B722" s="3"/>
+      <c r="B722" s="4"/>
     </row>
     <row r="723" customHeight="1" spans="2:2">
-      <c r="B723" s="3"/>
+      <c r="B723" s="4"/>
     </row>
     <row r="724" customHeight="1" spans="2:2">
-      <c r="B724" s="3"/>
+      <c r="B724" s="4"/>
     </row>
     <row r="725" customHeight="1" spans="2:2">
-      <c r="B725" s="3"/>
+      <c r="B725" s="4"/>
     </row>
     <row r="726" customHeight="1" spans="2:2">
-      <c r="B726" s="3"/>
+      <c r="B726" s="4"/>
     </row>
     <row r="727" customHeight="1" spans="2:2">
-      <c r="B727" s="3"/>
+      <c r="B727" s="4"/>
     </row>
     <row r="728" customHeight="1" spans="2:2">
-      <c r="B728" s="3"/>
+      <c r="B728" s="4"/>
     </row>
     <row r="729" customHeight="1" spans="2:2">
-      <c r="B729" s="3"/>
+      <c r="B729" s="4"/>
     </row>
     <row r="730" customHeight="1" spans="2:2">
-      <c r="B730" s="3"/>
+      <c r="B730" s="4"/>
     </row>
     <row r="731" customHeight="1" spans="2:2">
-      <c r="B731" s="3"/>
+      <c r="B731" s="4"/>
     </row>
     <row r="732" customHeight="1" spans="2:2">
-      <c r="B732" s="3"/>
+      <c r="B732" s="4"/>
     </row>
     <row r="733" customHeight="1" spans="2:2">
-      <c r="B733" s="3"/>
+      <c r="B733" s="4"/>
     </row>
     <row r="734" customHeight="1" spans="2:2">
-      <c r="B734" s="3"/>
+      <c r="B734" s="4"/>
     </row>
     <row r="735" customHeight="1" spans="2:2">
-      <c r="B735" s="3"/>
+      <c r="B735" s="4"/>
     </row>
     <row r="736" customHeight="1" spans="2:2">
-      <c r="B736" s="3"/>
+      <c r="B736" s="4"/>
     </row>
     <row r="737" customHeight="1" spans="2:2">
-      <c r="B737" s="3"/>
+      <c r="B737" s="4"/>
     </row>
     <row r="738" customHeight="1" spans="2:2">
-      <c r="B738" s="3"/>
+      <c r="B738" s="4"/>
     </row>
     <row r="739" customHeight="1" spans="2:2">
-      <c r="B739" s="3"/>
+      <c r="B739" s="4"/>
     </row>
     <row r="740" customHeight="1" spans="2:2">
-      <c r="B740" s="3"/>
+      <c r="B740" s="4"/>
     </row>
     <row r="741" customHeight="1" spans="2:2">
-      <c r="B741" s="3"/>
+      <c r="B741" s="4"/>
     </row>
     <row r="742" customHeight="1" spans="2:2">
-      <c r="B742" s="3"/>
+      <c r="B742" s="4"/>
     </row>
     <row r="743" customHeight="1" spans="2:2">
-      <c r="B743" s="3"/>
+      <c r="B743" s="4"/>
     </row>
     <row r="744" customHeight="1" spans="2:2">
-      <c r="B744" s="3"/>
+      <c r="B744" s="4"/>
     </row>
     <row r="745" customHeight="1" spans="2:2">
-      <c r="B745" s="3"/>
+      <c r="B745" s="4"/>
     </row>
     <row r="746" customHeight="1" spans="2:2">
-      <c r="B746" s="3"/>
+      <c r="B746" s="4"/>
     </row>
     <row r="747" customHeight="1" spans="2:2">
-      <c r="B747" s="3"/>
+      <c r="B747" s="4"/>
     </row>
     <row r="748" customHeight="1" spans="2:2">
-      <c r="B748" s="3"/>
+      <c r="B748" s="4"/>
     </row>
     <row r="749" customHeight="1" spans="2:2">
-      <c r="B749" s="3"/>
+      <c r="B749" s="4"/>
     </row>
     <row r="750" customHeight="1" spans="2:2">
-      <c r="B750" s="3"/>
+      <c r="B750" s="4"/>
     </row>
     <row r="751" customHeight="1" spans="2:2">
-      <c r="B751" s="3"/>
+      <c r="B751" s="4"/>
     </row>
     <row r="752" customHeight="1" spans="2:2">
-      <c r="B752" s="3"/>
+      <c r="B752" s="4"/>
     </row>
     <row r="753" customHeight="1" spans="2:2">
-      <c r="B753" s="3"/>
+      <c r="B753" s="4"/>
     </row>
     <row r="754" customHeight="1" spans="2:2">
-      <c r="B754" s="3"/>
+      <c r="B754" s="4"/>
     </row>
     <row r="755" customHeight="1" spans="2:2">
-      <c r="B755" s="3"/>
+      <c r="B755" s="4"/>
     </row>
     <row r="756" customHeight="1" spans="2:2">
-      <c r="B756" s="3"/>
+      <c r="B756" s="4"/>
     </row>
     <row r="757" customHeight="1" spans="2:2">
-      <c r="B757" s="3"/>
+      <c r="B757" s="4"/>
     </row>
     <row r="758" customHeight="1" spans="2:2">
-      <c r="B758" s="3"/>
+      <c r="B758" s="4"/>
     </row>
     <row r="759" customHeight="1" spans="2:2">
-      <c r="B759" s="3"/>
+      <c r="B759" s="4"/>
     </row>
     <row r="760" customHeight="1" spans="2:2">
-      <c r="B760" s="3"/>
+      <c r="B760" s="4"/>
     </row>
     <row r="761" customHeight="1" spans="2:2">
-      <c r="B761" s="3"/>
+      <c r="B761" s="4"/>
     </row>
     <row r="762" customHeight="1" spans="2:2">
-      <c r="B762" s="3"/>
+      <c r="B762" s="4"/>
     </row>
     <row r="763" customHeight="1" spans="2:2">
-      <c r="B763" s="3"/>
+      <c r="B763" s="4"/>
     </row>
     <row r="764" customHeight="1" spans="2:2">
-      <c r="B764" s="3"/>
+      <c r="B764" s="4"/>
     </row>
     <row r="765" customHeight="1" spans="2:2">
-      <c r="B765" s="3"/>
+      <c r="B765" s="4"/>
     </row>
     <row r="766" customHeight="1" spans="2:2">
-      <c r="B766" s="3"/>
+      <c r="B766" s="4"/>
     </row>
     <row r="767" customHeight="1" spans="2:2">
-      <c r="B767" s="3"/>
+      <c r="B767" s="4"/>
     </row>
     <row r="768" customHeight="1" spans="2:2">
-      <c r="B768" s="3"/>
+      <c r="B768" s="4"/>
     </row>
     <row r="769" customHeight="1" spans="2:2">
-      <c r="B769" s="3"/>
+      <c r="B769" s="4"/>
     </row>
     <row r="770" customHeight="1" spans="2:2">
-      <c r="B770" s="3"/>
+      <c r="B770" s="4"/>
     </row>
     <row r="771" customHeight="1" spans="2:2">
-      <c r="B771" s="3"/>
+      <c r="B771" s="4"/>
     </row>
     <row r="772" customHeight="1" spans="2:2">
-      <c r="B772" s="3"/>
+      <c r="B772" s="4"/>
     </row>
     <row r="773" customHeight="1" spans="2:2">
-      <c r="B773" s="3"/>
+      <c r="B773" s="4"/>
     </row>
     <row r="774" customHeight="1" spans="2:2">
-      <c r="B774" s="3"/>
+      <c r="B774" s="4"/>
     </row>
     <row r="775" customHeight="1" spans="2:2">
-      <c r="B775" s="3"/>
+      <c r="B775" s="4"/>
     </row>
     <row r="776" customHeight="1" spans="2:2">
-      <c r="B776" s="3"/>
+      <c r="B776" s="4"/>
     </row>
     <row r="777" customHeight="1" spans="2:2">
-      <c r="B777" s="3"/>
+      <c r="B777" s="4"/>
     </row>
     <row r="778" customHeight="1" spans="2:2">
-      <c r="B778" s="3"/>
+      <c r="B778" s="4"/>
     </row>
     <row r="779" customHeight="1" spans="2:2">
-      <c r="B779" s="3"/>
+      <c r="B779" s="4"/>
     </row>
     <row r="780" customHeight="1" spans="2:2">
-      <c r="B780" s="3"/>
+      <c r="B780" s="4"/>
     </row>
     <row r="781" customHeight="1" spans="2:2">
-      <c r="B781" s="3"/>
+      <c r="B781" s="4"/>
     </row>
     <row r="782" customHeight="1" spans="2:2">
-      <c r="B782" s="3"/>
+      <c r="B782" s="4"/>
     </row>
     <row r="783" customHeight="1" spans="2:2">
-      <c r="B783" s="3"/>
+      <c r="B783" s="4"/>
     </row>
     <row r="784" customHeight="1" spans="2:2">
-      <c r="B784" s="3"/>
+      <c r="B784" s="4"/>
     </row>
     <row r="785" customHeight="1" spans="2:2">
-      <c r="B785" s="3"/>
+      <c r="B785" s="4"/>
     </row>
     <row r="786" customHeight="1" spans="2:2">
-      <c r="B786" s="3"/>
+      <c r="B786" s="4"/>
     </row>
     <row r="787" customHeight="1" spans="2:2">
-      <c r="B787" s="3"/>
+      <c r="B787" s="4"/>
     </row>
     <row r="788" customHeight="1" spans="2:2">
-      <c r="B788" s="3"/>
+      <c r="B788" s="4"/>
     </row>
     <row r="789" customHeight="1" spans="2:2">
-      <c r="B789" s="3"/>
+      <c r="B789" s="4"/>
     </row>
     <row r="790" customHeight="1" spans="2:2">
-      <c r="B790" s="3"/>
+      <c r="B790" s="4"/>
     </row>
     <row r="791" customHeight="1" spans="2:2">
-      <c r="B791" s="3"/>
+      <c r="B791" s="4"/>
     </row>
     <row r="792" customHeight="1" spans="2:2">
-      <c r="B792" s="3"/>
+      <c r="B792" s="4"/>
     </row>
     <row r="793" customHeight="1" spans="2:2">
-      <c r="B793" s="3"/>
+      <c r="B793" s="4"/>
     </row>
     <row r="794" customHeight="1" spans="2:2">
-      <c r="B794" s="3"/>
+      <c r="B794" s="4"/>
     </row>
     <row r="795" customHeight="1" spans="2:2">
-      <c r="B795" s="3"/>
+      <c r="B795" s="4"/>
     </row>
     <row r="796" customHeight="1" spans="2:2">
-      <c r="B796" s="3"/>
+      <c r="B796" s="4"/>
     </row>
     <row r="797" customHeight="1" spans="2:2">
-      <c r="B797" s="3"/>
+      <c r="B797" s="4"/>
     </row>
     <row r="798" customHeight="1" spans="2:2">
-      <c r="B798" s="3"/>
+      <c r="B798" s="4"/>
     </row>
     <row r="799" customHeight="1" spans="2:2">
-      <c r="B799" s="3"/>
+      <c r="B799" s="4"/>
     </row>
     <row r="800" customHeight="1" spans="2:2">
-      <c r="B800" s="3"/>
+      <c r="B800" s="4"/>
     </row>
     <row r="801" customHeight="1" spans="2:2">
-      <c r="B801" s="3"/>
+      <c r="B801" s="4"/>
     </row>
     <row r="802" customHeight="1" spans="2:2">
-      <c r="B802" s="3"/>
+      <c r="B802" s="4"/>
     </row>
     <row r="803" customHeight="1" spans="2:2">
-      <c r="B803" s="3"/>
+      <c r="B803" s="4"/>
     </row>
     <row r="804" customHeight="1" spans="2:2">
-      <c r="B804" s="3"/>
+      <c r="B804" s="4"/>
     </row>
     <row r="805" customHeight="1" spans="2:2">
-      <c r="B805" s="3"/>
+      <c r="B805" s="4"/>
     </row>
     <row r="806" customHeight="1" spans="2:2">
-      <c r="B806" s="3"/>
+      <c r="B806" s="4"/>
     </row>
     <row r="807" customHeight="1" spans="2:2">
-      <c r="B807" s="3"/>
+      <c r="B807" s="4"/>
     </row>
     <row r="808" customHeight="1" spans="2:2">
-      <c r="B808" s="3"/>
+      <c r="B808" s="4"/>
     </row>
     <row r="809" customHeight="1" spans="2:2">
-      <c r="B809" s="3"/>
+      <c r="B809" s="4"/>
     </row>
     <row r="810" customHeight="1" spans="2:2">
-      <c r="B810" s="3"/>
+      <c r="B810" s="4"/>
     </row>
     <row r="811" customHeight="1" spans="2:2">
-      <c r="B811" s="3"/>
+      <c r="B811" s="4"/>
     </row>
     <row r="812" customHeight="1" spans="2:2">
-      <c r="B812" s="3"/>
+      <c r="B812" s="4"/>
     </row>
     <row r="813" customHeight="1" spans="2:2">
-      <c r="B813" s="3"/>
+      <c r="B813" s="4"/>
     </row>
     <row r="814" customHeight="1" spans="2:2">
-      <c r="B814" s="3"/>
+      <c r="B814" s="4"/>
     </row>
     <row r="815" customHeight="1" spans="2:2">
-      <c r="B815" s="3"/>
+      <c r="B815" s="4"/>
     </row>
     <row r="816" customHeight="1" spans="2:2">
-      <c r="B816" s="3"/>
+      <c r="B816" s="4"/>
     </row>
     <row r="817" customHeight="1" spans="2:2">
-      <c r="B817" s="3"/>
+      <c r="B817" s="4"/>
     </row>
     <row r="818" customHeight="1" spans="2:2">
-      <c r="B818" s="3"/>
+      <c r="B818" s="4"/>
     </row>
     <row r="819" customHeight="1" spans="2:2">
-      <c r="B819" s="3"/>
+      <c r="B819" s="4"/>
     </row>
     <row r="820" customHeight="1" spans="2:2">
-      <c r="B820" s="3"/>
+      <c r="B820" s="4"/>
     </row>
     <row r="821" customHeight="1" spans="2:2">
-      <c r="B821" s="3"/>
+      <c r="B821" s="4"/>
     </row>
     <row r="822" customHeight="1" spans="2:2">
-      <c r="B822" s="3"/>
+      <c r="B822" s="4"/>
     </row>
     <row r="823" customHeight="1" spans="2:2">
-      <c r="B823" s="3"/>
+      <c r="B823" s="4"/>
     </row>
     <row r="824" customHeight="1" spans="2:2">
-      <c r="B824" s="3"/>
+      <c r="B824" s="4"/>
     </row>
     <row r="825" customHeight="1" spans="2:2">
-      <c r="B825" s="3"/>
+      <c r="B825" s="4"/>
     </row>
     <row r="826" customHeight="1" spans="2:2">
-      <c r="B826" s="3"/>
+      <c r="B826" s="4"/>
     </row>
     <row r="827" customHeight="1" spans="2:2">
-      <c r="B827" s="3"/>
+      <c r="B827" s="4"/>
     </row>
     <row r="828" customHeight="1" spans="2:2">
-      <c r="B828" s="3"/>
+      <c r="B828" s="4"/>
     </row>
     <row r="829" customHeight="1" spans="2:2">
-      <c r="B829" s="3"/>
+      <c r="B829" s="4"/>
     </row>
     <row r="830" customHeight="1" spans="2:2">
-      <c r="B830" s="3"/>
+      <c r="B830" s="4"/>
     </row>
     <row r="831" customHeight="1" spans="2:2">
-      <c r="B831" s="3"/>
+      <c r="B831" s="4"/>
     </row>
     <row r="832" customHeight="1" spans="2:2">
-      <c r="B832" s="3"/>
+      <c r="B832" s="4"/>
     </row>
     <row r="833" customHeight="1" spans="2:2">
-      <c r="B833" s="3"/>
+      <c r="B833" s="4"/>
     </row>
     <row r="834" customHeight="1" spans="2:2">
-      <c r="B834" s="3"/>
+      <c r="B834" s="4"/>
     </row>
     <row r="835" customHeight="1" spans="2:2">
-      <c r="B835" s="3"/>
+      <c r="B835" s="4"/>
     </row>
     <row r="836" customHeight="1" spans="2:2">
-      <c r="B836" s="3"/>
+      <c r="B836" s="4"/>
     </row>
     <row r="837" customHeight="1" spans="2:2">
-      <c r="B837" s="3"/>
+      <c r="B837" s="4"/>
     </row>
     <row r="838" customHeight="1" spans="2:2">
-      <c r="B838" s="3"/>
+      <c r="B838" s="4"/>
     </row>
     <row r="839" customHeight="1" spans="2:2">
-      <c r="B839" s="3"/>
+      <c r="B839" s="4"/>
     </row>
     <row r="840" customHeight="1" spans="2:2">
-      <c r="B840" s="3"/>
+      <c r="B840" s="4"/>
     </row>
     <row r="841" customHeight="1" spans="2:2">
-      <c r="B841" s="3"/>
+      <c r="B841" s="4"/>
     </row>
     <row r="842" customHeight="1" spans="2:2">
-      <c r="B842" s="3"/>
+      <c r="B842" s="4"/>
     </row>
     <row r="843" customHeight="1" spans="2:2">
-      <c r="B843" s="3"/>
+      <c r="B843" s="4"/>
     </row>
     <row r="844" customHeight="1" spans="2:2">
-      <c r="B844" s="3"/>
+      <c r="B844" s="4"/>
     </row>
     <row r="845" customHeight="1" spans="2:2">
-      <c r="B845" s="3"/>
+      <c r="B845" s="4"/>
     </row>
     <row r="846" customHeight="1" spans="2:2">
-      <c r="B846" s="3"/>
+      <c r="B846" s="4"/>
     </row>
     <row r="847" customHeight="1" spans="2:2">
-      <c r="B847" s="3"/>
+      <c r="B847" s="4"/>
     </row>
     <row r="848" customHeight="1" spans="2:2">
-      <c r="B848" s="3"/>
+      <c r="B848" s="4"/>
     </row>
     <row r="849" customHeight="1" spans="2:2">
-      <c r="B849" s="3"/>
+      <c r="B849" s="4"/>
     </row>
     <row r="850" customHeight="1" spans="2:2">
-      <c r="B850" s="3"/>
+      <c r="B850" s="4"/>
     </row>
     <row r="851" customHeight="1" spans="2:2">
-      <c r="B851" s="3"/>
+      <c r="B851" s="4"/>
     </row>
     <row r="852" customHeight="1" spans="2:2">
-      <c r="B852" s="3"/>
+      <c r="B852" s="4"/>
     </row>
     <row r="853" customHeight="1" spans="2:2">
-      <c r="B853" s="3"/>
+      <c r="B853" s="4"/>
     </row>
     <row r="854" customHeight="1" spans="2:2">
-      <c r="B854" s="3"/>
+      <c r="B854" s="4"/>
     </row>
     <row r="855" customHeight="1" spans="2:2">
-      <c r="B855" s="3"/>
+      <c r="B855" s="4"/>
     </row>
     <row r="856" customHeight="1" spans="2:2">
-      <c r="B856" s="3"/>
+      <c r="B856" s="4"/>
     </row>
     <row r="857" customHeight="1" spans="2:2">
-      <c r="B857" s="3"/>
+      <c r="B857" s="4"/>
     </row>
     <row r="858" customHeight="1" spans="2:2">
-      <c r="B858" s="3"/>
+      <c r="B858" s="4"/>
     </row>
     <row r="859" customHeight="1" spans="2:2">
-      <c r="B859" s="3"/>
+      <c r="B859" s="4"/>
     </row>
     <row r="860" customHeight="1" spans="2:2">
-      <c r="B860" s="3"/>
+      <c r="B860" s="4"/>
     </row>
     <row r="861" customHeight="1" spans="2:2">
-      <c r="B861" s="3"/>
+      <c r="B861" s="4"/>
     </row>
     <row r="862" customHeight="1" spans="2:2">
-      <c r="B862" s="3"/>
+      <c r="B862" s="4"/>
     </row>
     <row r="863" customHeight="1" spans="2:2">
-      <c r="B863" s="3"/>
+      <c r="B863" s="4"/>
     </row>
     <row r="864" customHeight="1" spans="2:2">
-      <c r="B864" s="3"/>
+      <c r="B864" s="4"/>
     </row>
     <row r="865" customHeight="1" spans="2:2">
-      <c r="B865" s="3"/>
+      <c r="B865" s="4"/>
     </row>
     <row r="866" customHeight="1" spans="2:2">
-      <c r="B866" s="3"/>
+      <c r="B866" s="4"/>
     </row>
     <row r="867" customHeight="1" spans="2:2">
-      <c r="B867" s="3"/>
+      <c r="B867" s="4"/>
     </row>
     <row r="868" customHeight="1" spans="2:2">
-      <c r="B868" s="3"/>
+      <c r="B868" s="4"/>
     </row>
     <row r="869" customHeight="1" spans="2:2">
-      <c r="B869" s="3"/>
+      <c r="B869" s="4"/>
     </row>
     <row r="870" customHeight="1" spans="2:2">
-      <c r="B870" s="3"/>
+      <c r="B870" s="4"/>
     </row>
     <row r="871" customHeight="1" spans="2:2">
-      <c r="B871" s="3"/>
+      <c r="B871" s="4"/>
     </row>
     <row r="872" customHeight="1" spans="2:2">
-      <c r="B872" s="3"/>
+      <c r="B872" s="4"/>
     </row>
     <row r="873" customHeight="1" spans="2:2">
-      <c r="B873" s="3"/>
+      <c r="B873" s="4"/>
     </row>
     <row r="874" customHeight="1" spans="2:2">
-      <c r="B874" s="3"/>
+      <c r="B874" s="4"/>
     </row>
     <row r="875" customHeight="1" spans="2:2">
-      <c r="B875" s="3"/>
+      <c r="B875" s="4"/>
     </row>
     <row r="876" customHeight="1" spans="2:2">
-      <c r="B876" s="3"/>
+      <c r="B876" s="4"/>
     </row>
     <row r="877" customHeight="1" spans="2:2">
-      <c r="B877" s="3"/>
+      <c r="B877" s="4"/>
     </row>
     <row r="878" customHeight="1" spans="2:2">
-      <c r="B878" s="3"/>
+      <c r="B878" s="4"/>
     </row>
     <row r="879" customHeight="1" spans="2:2">
-      <c r="B879" s="3"/>
+      <c r="B879" s="4"/>
     </row>
     <row r="880" customHeight="1" spans="2:2">
-      <c r="B880" s="3"/>
+      <c r="B880" s="4"/>
     </row>
     <row r="881" customHeight="1" spans="2:2">
-      <c r="B881" s="3"/>
+      <c r="B881" s="4"/>
     </row>
     <row r="882" customHeight="1" spans="2:2">
-      <c r="B882" s="3"/>
+      <c r="B882" s="4"/>
     </row>
     <row r="883" customHeight="1" spans="2:2">
-      <c r="B883" s="3"/>
+      <c r="B883" s="4"/>
     </row>
     <row r="884" customHeight="1" spans="2:2">
-      <c r="B884" s="3"/>
+      <c r="B884" s="4"/>
     </row>
     <row r="885" customHeight="1" spans="2:2">
-      <c r="B885" s="3"/>
+      <c r="B885" s="4"/>
     </row>
     <row r="886" customHeight="1" spans="2:2">
-      <c r="B886" s="3"/>
+      <c r="B886" s="4"/>
     </row>
     <row r="887" customHeight="1" spans="2:2">
-      <c r="B887" s="3"/>
+      <c r="B887" s="4"/>
     </row>
     <row r="888" customHeight="1" spans="2:2">
-      <c r="B888" s="3"/>
+      <c r="B888" s="4"/>
     </row>
     <row r="889" customHeight="1" spans="2:2">
-      <c r="B889" s="3"/>
+      <c r="B889" s="4"/>
     </row>
     <row r="890" customHeight="1" spans="2:2">
-      <c r="B890" s="3"/>
+      <c r="B890" s="4"/>
     </row>
     <row r="891" customHeight="1" spans="2:2">
-      <c r="B891" s="3"/>
+      <c r="B891" s="4"/>
     </row>
     <row r="892" customHeight="1" spans="2:2">
-      <c r="B892" s="3"/>
+      <c r="B892" s="4"/>
     </row>
     <row r="893" customHeight="1" spans="2:2">
-      <c r="B893" s="3"/>
+      <c r="B893" s="4"/>
     </row>
     <row r="894" customHeight="1" spans="2:2">
-      <c r="B894" s="3"/>
+      <c r="B894" s="4"/>
     </row>
     <row r="895" customHeight="1" spans="2:2">
-      <c r="B895" s="3"/>
+      <c r="B895" s="4"/>
     </row>
     <row r="896" customHeight="1" spans="2:2">
-      <c r="B896" s="3"/>
+      <c r="B896" s="4"/>
     </row>
     <row r="897" customHeight="1" spans="2:2">
-      <c r="B897" s="3"/>
+      <c r="B897" s="4"/>
     </row>
     <row r="898" customHeight="1" spans="2:2">
-      <c r="B898" s="3"/>
+      <c r="B898" s="4"/>
     </row>
     <row r="899" customHeight="1" spans="2:2">
-      <c r="B899" s="3"/>
+      <c r="B899" s="4"/>
     </row>
     <row r="900" customHeight="1" spans="2:2">
-      <c r="B900" s="3"/>
+      <c r="B900" s="4"/>
     </row>
     <row r="901" customHeight="1" spans="2:2">
-      <c r="B901" s="3"/>
+      <c r="B901" s="4"/>
     </row>
     <row r="902" customHeight="1" spans="2:2">
-      <c r="B902" s="3"/>
+      <c r="B902" s="4"/>
     </row>
     <row r="903" customHeight="1" spans="2:2">
-      <c r="B903" s="3"/>
+      <c r="B903" s="4"/>
     </row>
     <row r="904" customHeight="1" spans="2:2">
-      <c r="B904" s="3"/>
+      <c r="B904" s="4"/>
     </row>
     <row r="905" customHeight="1" spans="2:2">
-      <c r="B905" s="3"/>
+      <c r="B905" s="4"/>
     </row>
     <row r="906" customHeight="1" spans="2:2">
-      <c r="B906" s="3"/>
+      <c r="B906" s="4"/>
     </row>
     <row r="907" customHeight="1" spans="2:2">
-      <c r="B907" s="3"/>
+      <c r="B907" s="4"/>
     </row>
     <row r="908" customHeight="1" spans="2:2">
-      <c r="B908" s="3"/>
+      <c r="B908" s="4"/>
     </row>
     <row r="909" customHeight="1" spans="2:2">
-      <c r="B909" s="3"/>
+      <c r="B909" s="4"/>
     </row>
     <row r="910" customHeight="1" spans="2:2">
-      <c r="B910" s="3"/>
+      <c r="B910" s="4"/>
     </row>
     <row r="911" customHeight="1" spans="2:2">
-      <c r="B911" s="3"/>
+      <c r="B911" s="4"/>
     </row>
     <row r="912" customHeight="1" spans="2:2">
-      <c r="B912" s="3"/>
+      <c r="B912" s="4"/>
     </row>
     <row r="913" customHeight="1" spans="2:2">
-      <c r="B913" s="3"/>
+      <c r="B913" s="4"/>
     </row>
     <row r="914" customHeight="1" spans="2:2">
-      <c r="B914" s="3"/>
+      <c r="B914" s="4"/>
     </row>
     <row r="915" customHeight="1" spans="2:2">
-      <c r="B915" s="3"/>
+      <c r="B915" s="4"/>
     </row>
     <row r="916" customHeight="1" spans="2:2">
-      <c r="B916" s="3"/>
+      <c r="B916" s="4"/>
     </row>
     <row r="917" customHeight="1" spans="2:2">
-      <c r="B917" s="3"/>
+      <c r="B917" s="4"/>
     </row>
     <row r="918" customHeight="1" spans="2:2">
-      <c r="B918" s="3"/>
+      <c r="B918" s="4"/>
     </row>
     <row r="919" customHeight="1" spans="2:2">
-      <c r="B919" s="3"/>
+      <c r="B919" s="4"/>
     </row>
     <row r="920" customHeight="1" spans="2:2">
-      <c r="B920" s="3"/>
+      <c r="B920" s="4"/>
     </row>
     <row r="921" customHeight="1" spans="2:2">
-      <c r="B921" s="3"/>
+      <c r="B921" s="4"/>
     </row>
     <row r="922" customHeight="1" spans="2:2">
-      <c r="B922" s="3"/>
+      <c r="B922" s="4"/>
     </row>
     <row r="923" customHeight="1" spans="2:2">
-      <c r="B923" s="3"/>
+      <c r="B923" s="4"/>
     </row>
     <row r="924" customHeight="1" spans="2:2">
-      <c r="B924" s="3"/>
+      <c r="B924" s="4"/>
     </row>
     <row r="925" customHeight="1" spans="2:2">
-      <c r="B925" s="3"/>
+      <c r="B925" s="4"/>
     </row>
     <row r="926" customHeight="1" spans="2:2">
-      <c r="B926" s="3"/>
+      <c r="B926" s="4"/>
     </row>
     <row r="927" customHeight="1" spans="2:2">
-      <c r="B927" s="3"/>
+      <c r="B927" s="4"/>
     </row>
     <row r="928" customHeight="1" spans="2:2">
-      <c r="B928" s="3"/>
+      <c r="B928" s="4"/>
     </row>
     <row r="929" customHeight="1" spans="2:2">
-      <c r="B929" s="3"/>
+      <c r="B929" s="4"/>
     </row>
     <row r="930" customHeight="1" spans="2:2">
-      <c r="B930" s="3"/>
+      <c r="B930" s="4"/>
     </row>
     <row r="931" customHeight="1" spans="2:2">
-      <c r="B931" s="3"/>
+      <c r="B931" s="4"/>
     </row>
     <row r="932" customHeight="1" spans="2:2">
-      <c r="B932" s="3"/>
+      <c r="B932" s="4"/>
     </row>
     <row r="933" customHeight="1" spans="2:2">
-      <c r="B933" s="3"/>
+      <c r="B933" s="4"/>
     </row>
     <row r="934" customHeight="1" spans="2:2">
-      <c r="B934" s="3"/>
+      <c r="B934" s="4"/>
     </row>
     <row r="935" customHeight="1" spans="2:2">
-      <c r="B935" s="3"/>
+      <c r="B935" s="4"/>
     </row>
     <row r="936" customHeight="1" spans="2:2">
-      <c r="B936" s="3"/>
+      <c r="B936" s="4"/>
     </row>
     <row r="937" customHeight="1" spans="2:2">
-      <c r="B937" s="3"/>
+      <c r="B937" s="4"/>
     </row>
     <row r="938" customHeight="1" spans="2:2">
-      <c r="B938" s="3"/>
+      <c r="B938" s="4"/>
     </row>
     <row r="939" customHeight="1" spans="2:2">
-      <c r="B939" s="3"/>
+      <c r="B939" s="4"/>
     </row>
     <row r="940" customHeight="1" spans="2:2">
-      <c r="B940" s="3"/>
+      <c r="B940" s="4"/>
     </row>
     <row r="941" customHeight="1" spans="2:2">
-      <c r="B941" s="3"/>
+      <c r="B941" s="4"/>
     </row>
     <row r="942" customHeight="1" spans="2:2">
-      <c r="B942" s="3"/>
+      <c r="B942" s="4"/>
     </row>
     <row r="943" customHeight="1" spans="2:2">
-      <c r="B943" s="3"/>
+      <c r="B943" s="4"/>
     </row>
     <row r="944" customHeight="1" spans="2:2">
-      <c r="B944" s="3"/>
+      <c r="B944" s="4"/>
     </row>
     <row r="945" customHeight="1" spans="2:2">
-      <c r="B945" s="3"/>
+      <c r="B945" s="4"/>
     </row>
     <row r="946" customHeight="1" spans="2:2">
-      <c r="B946" s="3"/>
+      <c r="B946" s="4"/>
     </row>
     <row r="947" customHeight="1" spans="2:2">
-      <c r="B947" s="3"/>
+      <c r="B947" s="4"/>
     </row>
     <row r="948" customHeight="1" spans="2:2">
-      <c r="B948" s="3"/>
+      <c r="B948" s="4"/>
     </row>
     <row r="949" customHeight="1" spans="2:2">
-      <c r="B949" s="3"/>
+      <c r="B949" s="4"/>
     </row>
     <row r="950" customHeight="1" spans="2:2">
-      <c r="B950" s="3"/>
+      <c r="B950" s="4"/>
     </row>
     <row r="951" customHeight="1" spans="2:2">
-      <c r="B951" s="3"/>
+      <c r="B951" s="4"/>
     </row>
     <row r="952" customHeight="1" spans="2:2">
-      <c r="B952" s="3"/>
+      <c r="B952" s="4"/>
     </row>
     <row r="953" customHeight="1" spans="2:2">
-      <c r="B953" s="3"/>
+      <c r="B953" s="4"/>
     </row>
     <row r="954" customHeight="1" spans="2:2">
-      <c r="B954" s="3"/>
+      <c r="B954" s="4"/>
     </row>
     <row r="955" customHeight="1" spans="2:2">
-      <c r="B955" s="3"/>
+      <c r="B955" s="4"/>
     </row>
     <row r="956" customHeight="1" spans="2:2">
-      <c r="B956" s="3"/>
+      <c r="B956" s="4"/>
     </row>
     <row r="957" customHeight="1" spans="2:2">
-      <c r="B957" s="3"/>
+      <c r="B957" s="4"/>
     </row>
     <row r="958" customHeight="1" spans="2:2">
-      <c r="B958" s="3"/>
+      <c r="B958" s="4"/>
     </row>
     <row r="959" customHeight="1" spans="2:2">
-      <c r="B959" s="3"/>
+      <c r="B959" s="4"/>
     </row>
     <row r="960" customHeight="1" spans="2:2">
-      <c r="B960" s="3"/>
+      <c r="B960" s="4"/>
     </row>
     <row r="961" customHeight="1" spans="2:2">
-      <c r="B961" s="3"/>
+      <c r="B961" s="4"/>
     </row>
     <row r="962" customHeight="1" spans="2:2">
-      <c r="B962" s="3"/>
+      <c r="B962" s="4"/>
     </row>
     <row r="963" customHeight="1" spans="2:2">
-      <c r="B963" s="3"/>
+      <c r="B963" s="4"/>
     </row>
     <row r="964" customHeight="1" spans="2:2">
-      <c r="B964" s="3"/>
+      <c r="B964" s="4"/>
     </row>
     <row r="965" customHeight="1" spans="2:2">
-      <c r="B965" s="3"/>
+      <c r="B965" s="4"/>
     </row>
     <row r="966" customHeight="1" spans="2:2">
-      <c r="B966" s="3"/>
+      <c r="B966" s="4"/>
     </row>
     <row r="967" customHeight="1" spans="2:2">
-      <c r="B967" s="3"/>
+      <c r="B967" s="4"/>
     </row>
     <row r="968" customHeight="1" spans="2:2">
-      <c r="B968" s="3"/>
+      <c r="B968" s="4"/>
     </row>
     <row r="969" customHeight="1" spans="2:2">
-      <c r="B969" s="3"/>
+      <c r="B969" s="4"/>
     </row>
     <row r="970" customHeight="1" spans="2:2">
-      <c r="B970" s="3"/>
+      <c r="B970" s="4"/>
     </row>
     <row r="971" customHeight="1" spans="2:2">
-      <c r="B971" s="3"/>
+      <c r="B971" s="4"/>
     </row>
     <row r="972" customHeight="1" spans="2:2">
-      <c r="B972" s="3"/>
+      <c r="B972" s="4"/>
     </row>
     <row r="973" customHeight="1" spans="2:2">
-      <c r="B973" s="3"/>
+      <c r="B973" s="4"/>
     </row>
     <row r="974" customHeight="1" spans="2:2">
-      <c r="B974" s="3"/>
+      <c r="B974" s="4"/>
     </row>
     <row r="975" customHeight="1" spans="2:2">
-      <c r="B975" s="3"/>
+      <c r="B975" s="4"/>
     </row>
     <row r="976" customHeight="1" spans="2:2">
-      <c r="B976" s="3"/>
+      <c r="B976" s="4"/>
     </row>
     <row r="977" customHeight="1" spans="2:2">
-      <c r="B977" s="3"/>
+      <c r="B977" s="4"/>
     </row>
     <row r="978" customHeight="1" spans="2:2">
-      <c r="B978" s="3"/>
+      <c r="B978" s="4"/>
     </row>
     <row r="979" customHeight="1" spans="2:2">
-      <c r="B979" s="3"/>
+      <c r="B979" s="4"/>
     </row>
     <row r="980" customHeight="1" spans="2:2">
-      <c r="B980" s="3"/>
+      <c r="B980" s="4"/>
     </row>
     <row r="981" customHeight="1" spans="2:2">
-      <c r="B981" s="3"/>
+      <c r="B981" s="4"/>
     </row>
     <row r="982" customHeight="1" spans="2:2">
-      <c r="B982" s="3"/>
+      <c r="B982" s="4"/>
     </row>
     <row r="983" customHeight="1" spans="2:2">
-      <c r="B983" s="3"/>
+      <c r="B983" s="4"/>
     </row>
     <row r="984" customHeight="1" spans="2:2">
-      <c r="B984" s="3"/>
+      <c r="B984" s="4"/>
     </row>
     <row r="985" customHeight="1" spans="2:2">
-      <c r="B985" s="3"/>
+      <c r="B985" s="4"/>
     </row>
     <row r="986" customHeight="1" spans="2:2">
-      <c r="B986" s="3"/>
+      <c r="B986" s="4"/>
     </row>
     <row r="987" customHeight="1" spans="2:2">
-      <c r="B987" s="3"/>
+      <c r="B987" s="4"/>
     </row>
     <row r="988" customHeight="1" spans="2:2">
-      <c r="B988" s="3"/>
+      <c r="B988" s="4"/>
     </row>
     <row r="989" customHeight="1" spans="2:2">
-      <c r="B989" s="3"/>
+      <c r="B989" s="4"/>
     </row>
     <row r="990" customHeight="1" spans="2:2">
-      <c r="B990" s="3"/>
+      <c r="B990" s="4"/>
     </row>
     <row r="991" customHeight="1" spans="2:2">
-      <c r="B991" s="3"/>
+      <c r="B991" s="4"/>
     </row>
     <row r="992" customHeight="1" spans="2:2">
-      <c r="B992" s="3"/>
+      <c r="B992" s="4"/>
     </row>
     <row r="993" customHeight="1" spans="2:2">
-      <c r="B993" s="3"/>
+      <c r="B993" s="4"/>
     </row>
     <row r="994" customHeight="1" spans="2:2">
-      <c r="B994" s="3"/>
+      <c r="B994" s="4"/>
     </row>
     <row r="995" customHeight="1" spans="2:2">
-      <c r="B995" s="3"/>
+      <c r="B995" s="4"/>
     </row>
     <row r="996" customHeight="1" spans="2:2">
-      <c r="B996" s="3"/>
+      <c r="B996" s="4"/>
     </row>
     <row r="997" customHeight="1" spans="2:2">
-      <c r="B997" s="3"/>
+      <c r="B997" s="4"/>
     </row>
     <row r="998" customHeight="1" spans="2:2">
-      <c r="B998" s="3"/>
+      <c r="B998" s="4"/>
     </row>
     <row r="999" customHeight="1" spans="2:2">
-      <c r="B999" s="3"/>
+      <c r="B999" s="4"/>
     </row>
     <row r="1000" customHeight="1" spans="2:2">
-      <c r="B1000" s="3"/>
+      <c r="B1000" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/products.xlsx
+++ b/products.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="123">
   <si>
     <t>ID</t>
   </si>
@@ -255,6 +255,147 @@
   </si>
   <si>
     <t>LTGREYCLOUD</t>
+  </si>
+  <si>
+    <t>GUESS</t>
+  </si>
+  <si>
+    <t>NA-1</t>
+  </si>
+  <si>
+    <t>LADIES VEST</t>
+  </si>
+  <si>
+    <t>GREEN</t>
+  </si>
+  <si>
+    <t>Ladies, Vest, Outerwear</t>
+  </si>
+  <si>
+    <t>NA-2</t>
+  </si>
+  <si>
+    <t>LADIES DRAPE TOP</t>
+  </si>
+  <si>
+    <t>PINK</t>
+  </si>
+  <si>
+    <t>Ladies, Top, Drape</t>
+  </si>
+  <si>
+    <t>NA-3</t>
+  </si>
+  <si>
+    <t>LADIES RUFFLE-FLY NECK TANK TOP</t>
+  </si>
+  <si>
+    <t>PURPLE</t>
+  </si>
+  <si>
+    <t>Ladies, Tank Top, Ruffle</t>
+  </si>
+  <si>
+    <t>W01319-J44P0-B425-N</t>
+  </si>
+  <si>
+    <t>LADIES TOP</t>
+  </si>
+  <si>
+    <t>Ladies, Top</t>
+  </si>
+  <si>
+    <t>NA-4</t>
+  </si>
+  <si>
+    <t>BLUE</t>
+  </si>
+  <si>
+    <t>W31I45K21W0</t>
+  </si>
+  <si>
+    <t>GUESS KID</t>
+  </si>
+  <si>
+    <t>N01342-I3LI0</t>
+  </si>
+  <si>
+    <t>BOY POLO</t>
+  </si>
+  <si>
+    <t>NAVY</t>
+  </si>
+  <si>
+    <t>Kid, Boys, Polo</t>
+  </si>
+  <si>
+    <t>K01530-I3MQ0-B436-N</t>
+  </si>
+  <si>
+    <t>GIRL JACKET</t>
+  </si>
+  <si>
+    <t>Kid, Girls, Jacket</t>
+  </si>
+  <si>
+    <t>N01341-I3LI0</t>
+  </si>
+  <si>
+    <t>NA-5</t>
+  </si>
+  <si>
+    <t>GREY</t>
+  </si>
+  <si>
+    <t>J01351-I3QI0-001-N</t>
+  </si>
+  <si>
+    <t>GIRL TEE</t>
+  </si>
+  <si>
+    <t>WHITE</t>
+  </si>
+  <si>
+    <t>Kid, Girls, T-Shirt</t>
+  </si>
+  <si>
+    <t>J01355-I3QI0-B713-N</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>J01356-I3QI0-C457-N</t>
+  </si>
+  <si>
+    <t>GIRL SKIRT</t>
+  </si>
+  <si>
+    <t>Kid, Girls, Skirt, Bottoms</t>
+  </si>
+  <si>
+    <t>54_5</t>
+  </si>
+  <si>
+    <t>L01538I3MQ0-001-N</t>
+  </si>
+  <si>
+    <t>Kid, Girls, Jacket, Outerwear</t>
+  </si>
+  <si>
+    <t>NA-6</t>
+  </si>
+  <si>
+    <t>BOY JACKET</t>
+  </si>
+  <si>
+    <t>Kid, Boys, Jacket, Outerwear</t>
+  </si>
+  <si>
+    <t>L04532-I3MQ0-B446-N</t>
+  </si>
+  <si>
+    <t>L04534-I9AQ0-B446-N</t>
   </si>
 </sst>
 </file>
@@ -267,7 +408,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -300,6 +441,12 @@
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <color rgb="FF0F1115"/>
+      <name val="Menlo"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -756,31 +903,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -789,119 +933,122 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -924,6 +1071,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1399,7 +1547,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O1000"/>
+  <dimension ref="A1:O999"/>
   <sheetFormatPr defaultColWidth="12.6339285714286" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
@@ -1611,7 +1759,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="4" t="str">
-        <f t="shared" ref="B7:B13" si="0">A7&amp;D7&amp;"_"&amp;F7</f>
+        <f t="shared" ref="B7:B17" si="0">A7&amp;D7&amp;"_"&amp;F7</f>
         <v>13AS151000_GREYMELANGE+OLDROSE</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -1820,7 +1968,7 @@
         <v>46</v>
       </c>
       <c r="B14" s="4" t="str">
-        <f>A14&amp;D14&amp;"_"&amp;F14</f>
+        <f t="shared" si="0"/>
         <v>19_5MS14-1063_POWEREDROSESORBET</v>
       </c>
       <c r="C14" s="5" t="s">
@@ -1850,7 +1998,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="4" t="str">
-        <f>A15&amp;D15&amp;"_"&amp;F15</f>
+        <f t="shared" si="0"/>
         <v>20MS14-1063_PINE</v>
       </c>
       <c r="C15" s="5" t="s">
@@ -1877,7 +2025,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="4" t="str">
-        <f>A16&amp;D16&amp;"_"&amp;F16</f>
+        <f t="shared" si="0"/>
         <v>21MS14-1069_LIGHTGREY</v>
       </c>
       <c r="C16" s="5" t="s">
@@ -1904,7 +2052,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="4" t="str">
-        <f>A17&amp;D17&amp;"_"&amp;F17</f>
+        <f t="shared" si="0"/>
         <v>22MS14-1069_POWDEREDROSESORBET</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -2443,87 +2591,501 @@
       <c r="A37" s="1">
         <v>42</v>
       </c>
-      <c r="B37" s="4"/>
+      <c r="B37" s="4" t="str">
+        <f>A37&amp;D37&amp;"_"&amp;F37</f>
+        <v>42NA-1_GREEN</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H37" s="1">
+        <v>1</v>
+      </c>
+      <c r="N37" s="8" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="38" customHeight="1" spans="1:14">
-      <c r="B38" s="4"/>
+      <c r="A38" s="1">
+        <v>43</v>
+      </c>
+      <c r="B38" s="4" t="str">
+        <f t="shared" ref="B37:B53" si="4">A38&amp;D38&amp;"_"&amp;F38</f>
+        <v>43NA-2_PINK</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1</v>
+      </c>
+      <c r="N38" s="8" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="39" customHeight="1" spans="1:14">
-      <c r="B39" s="4"/>
+      <c r="A39" s="1">
+        <v>44</v>
+      </c>
+      <c r="B39" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>44NA-3_PURPLE</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H39" s="1">
+        <v>1</v>
+      </c>
+      <c r="N39" s="8" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="40" customHeight="1" spans="1:14">
-      <c r="B40" s="4"/>
+      <c r="A40" s="1">
+        <v>45</v>
+      </c>
+      <c r="B40" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>45W01319-J44P0-B425-N_PINK</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H40" s="1">
+        <v>1</v>
+      </c>
+      <c r="N40" s="8" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="41" customHeight="1" spans="1:14">
-      <c r="B41" s="4"/>
+      <c r="A41" s="1">
+        <v>46</v>
+      </c>
+      <c r="B41" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>46NA-4_BLUE</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1</v>
+      </c>
+      <c r="N41" s="8" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="42" customHeight="1" spans="1:14">
-      <c r="B42" s="4"/>
+      <c r="A42" s="1">
+        <v>47</v>
+      </c>
+      <c r="B42" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>47W31I45K21W0_BLUE</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H42" s="1">
+        <v>1</v>
+      </c>
+      <c r="N42" s="8" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="43" customHeight="1" spans="1:14">
-      <c r="B43" s="4"/>
+      <c r="A43" s="1">
+        <v>48</v>
+      </c>
+      <c r="B43" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>48N01342-I3LI0_NAVY</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H43" s="1">
+        <v>1</v>
+      </c>
+      <c r="N43" s="8" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="44" customHeight="1" spans="1:14">
-      <c r="B44" s="4"/>
+      <c r="A44" s="1">
+        <v>49</v>
+      </c>
+      <c r="B44" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>49K01530-I3MQ0-B436-N_PINK</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H44" s="1">
+        <v>1</v>
+      </c>
+      <c r="N44" s="8" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="45" customHeight="1" spans="1:14">
-      <c r="B45" s="4"/>
+      <c r="A45" s="1">
+        <v>50</v>
+      </c>
+      <c r="B45" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>50N01341-I3LI0_BLUE</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I45" s="1">
+        <v>1</v>
+      </c>
+      <c r="N45" s="8" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="46" customHeight="1" spans="1:14">
-      <c r="B46" s="4"/>
+      <c r="A46" s="1">
+        <v>51</v>
+      </c>
+      <c r="B46" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>51NA-5_GREY</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1</v>
+      </c>
+      <c r="N46" s="8" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="47" customHeight="1" spans="1:14">
-      <c r="B47" s="4"/>
+      <c r="A47" s="1">
+        <v>52</v>
+      </c>
+      <c r="B47" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>52J01351-I3QI0-001-N_WHITE</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H47" s="1">
+        <v>1</v>
+      </c>
+      <c r="N47" s="8" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="48" customHeight="1" spans="1:14">
-      <c r="B48" s="4"/>
-    </row>
-    <row r="49" customHeight="1" spans="2:2">
-      <c r="B49" s="4"/>
-    </row>
-    <row r="50" customHeight="1" spans="2:2">
-      <c r="B50" s="4"/>
-    </row>
-    <row r="51" customHeight="1" spans="2:2">
-      <c r="B51" s="4"/>
-    </row>
-    <row r="52" customHeight="1" spans="2:2">
-      <c r="B52" s="4"/>
-    </row>
-    <row r="53" customHeight="1" spans="2:2">
-      <c r="B53" s="4"/>
-    </row>
-    <row r="54" customHeight="1" spans="2:2">
+      <c r="A48" s="1">
+        <v>53</v>
+      </c>
+      <c r="B48" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>53J01355-I3QI0-B713-N_BLACK</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I48" s="1">
+        <v>1</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="N48" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="1:14">
+      <c r="A49" s="1">
+        <v>54</v>
+      </c>
+      <c r="B49" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>54J01356-I3QI0-C457-N_PURPLE</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J49" s="1">
+        <v>1</v>
+      </c>
+      <c r="N49" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="1:14">
+      <c r="A50" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B50" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>54_5L01538I3MQ0-001-N_WHITE</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H50" s="1">
+        <v>1</v>
+      </c>
+      <c r="N50" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="1:14">
+      <c r="A51" s="1">
+        <v>55</v>
+      </c>
+      <c r="B51" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>55NA-6_BLACK</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I51" s="1">
+        <v>1</v>
+      </c>
+      <c r="N51" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="1:14">
+      <c r="A52" s="1">
+        <v>56</v>
+      </c>
+      <c r="B52" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>56L04532-I3MQ0-B446-N_PURPLE</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I52" s="1">
+        <v>1</v>
+      </c>
+      <c r="N52" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="1:14">
+      <c r="A53" s="1">
+        <v>57</v>
+      </c>
+      <c r="B53" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v>57L04534-I9AQ0-B446-N_PURPLE</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I53" s="1">
+        <v>1</v>
+      </c>
+      <c r="N53" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="1:14">
       <c r="B54" s="4"/>
     </row>
-    <row r="55" customHeight="1" spans="2:2">
+    <row r="55" customHeight="1" spans="1:14">
       <c r="B55" s="4"/>
     </row>
-    <row r="56" customHeight="1" spans="2:2">
+    <row r="56" customHeight="1" spans="1:14">
       <c r="B56" s="4"/>
     </row>
-    <row r="57" customHeight="1" spans="2:2">
+    <row r="57" customHeight="1" spans="1:14">
       <c r="B57" s="4"/>
     </row>
-    <row r="58" customHeight="1" spans="2:2">
+    <row r="58" customHeight="1" spans="1:14">
       <c r="B58" s="4"/>
     </row>
-    <row r="59" customHeight="1" spans="2:2">
+    <row r="59" customHeight="1" spans="1:14">
       <c r="B59" s="4"/>
     </row>
-    <row r="60" customHeight="1" spans="2:2">
+    <row r="60" customHeight="1" spans="1:14">
       <c r="B60" s="4"/>
     </row>
-    <row r="61" customHeight="1" spans="2:2">
+    <row r="61" customHeight="1" spans="1:14">
       <c r="B61" s="4"/>
     </row>
-    <row r="62" customHeight="1" spans="2:2">
+    <row r="62" customHeight="1" spans="1:14">
       <c r="B62" s="4"/>
     </row>
-    <row r="63" customHeight="1" spans="2:2">
+    <row r="63" customHeight="1" spans="1:14">
       <c r="B63" s="4"/>
     </row>
-    <row r="64" customHeight="1" spans="2:2">
+    <row r="64" customHeight="1" spans="1:14">
       <c r="B64" s="4"/>
     </row>
     <row r="65" customHeight="1" spans="2:2">
@@ -5330,9 +5892,6 @@
     </row>
     <row r="999" customHeight="1" spans="2:2">
       <c r="B999" s="4"/>
-    </row>
-    <row r="1000" customHeight="1" spans="2:2">
-      <c r="B1000" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/products.xlsx
+++ b/products.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="140">
   <si>
     <t>ID</t>
   </si>
@@ -396,6 +396,57 @@
   </si>
   <si>
     <t>L04534-I9AQ0-B446-N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESTINO </t>
+  </si>
+  <si>
+    <t>NA-7</t>
+  </si>
+  <si>
+    <t>Jogger - 100 modal</t>
+  </si>
+  <si>
+    <t>Bottoms</t>
+  </si>
+  <si>
+    <t>NA-8</t>
+  </si>
+  <si>
+    <t>shorts -100 modal</t>
+  </si>
+  <si>
+    <t>NA-9</t>
+  </si>
+  <si>
+    <t>v-neck top - 100 modal</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>NA-10</t>
+  </si>
+  <si>
+    <t>full zip hoody - 100 modal</t>
+  </si>
+  <si>
+    <t>Top, Hoody</t>
+  </si>
+  <si>
+    <t>NA-11</t>
+  </si>
+  <si>
+    <t>tank top - two tone - 100 modal</t>
+  </si>
+  <si>
+    <t>NA-12</t>
+  </si>
+  <si>
+    <t>tank top - 100 modal</t>
+  </si>
+  <si>
+    <t>NA-13</t>
   </si>
 </sst>
 </file>
@@ -1554,7 +1605,7 @@
     <col min="2" max="2" width="29.3303571428571" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.6339285714286" style="1"/>
     <col min="4" max="4" width="11.0714285714286" style="1" customWidth="1"/>
-    <col min="5" max="5" width="60.6696428571429" style="1" customWidth="1"/>
+    <col min="5" max="5" width="41.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="26.5446428571429" style="1" customWidth="1"/>
     <col min="7" max="12" width="5.58035714285714" style="1" customWidth="1"/>
     <col min="13" max="13" width="6.58035714285714" style="1" customWidth="1"/>
@@ -2403,7 +2454,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="4" t="str">
-        <f t="shared" ref="B30:B36" si="3">A30&amp;D30&amp;"_"&amp;F30</f>
+        <f t="shared" ref="B30:B37" si="3">A30&amp;D30&amp;"_"&amp;F30</f>
         <v>35MS14-1061_PINE</v>
       </c>
       <c r="C30" s="5" t="s">
@@ -2592,7 +2643,7 @@
         <v>42</v>
       </c>
       <c r="B37" s="4" t="str">
-        <f>A37&amp;D37&amp;"_"&amp;F37</f>
+        <f t="shared" si="3"/>
         <v>42NA-1_GREEN</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -3056,25 +3107,160 @@
       </c>
     </row>
     <row r="54" customHeight="1" spans="1:14">
-      <c r="B54" s="4"/>
+      <c r="A54" s="1">
+        <v>1</v>
+      </c>
+      <c r="B54" s="4" t="str">
+        <f>A54&amp;D54</f>
+        <v>1NA-7</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H54" s="1">
+        <v>1</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="55" customHeight="1" spans="1:14">
-      <c r="B55" s="4"/>
+      <c r="A55" s="1">
+        <v>2</v>
+      </c>
+      <c r="B55" s="4" t="str">
+        <f>A55&amp;D55</f>
+        <v>2NA-8</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H55" s="1">
+        <v>1</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="56" customHeight="1" spans="1:14">
-      <c r="B56" s="4"/>
+      <c r="A56" s="1">
+        <v>3</v>
+      </c>
+      <c r="B56" s="4" t="str">
+        <f>A56&amp;D56</f>
+        <v>3NA-9</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H56" s="1">
+        <v>1</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="57" customHeight="1" spans="1:14">
-      <c r="B57" s="4"/>
+      <c r="A57" s="1">
+        <v>4</v>
+      </c>
+      <c r="B57" s="4" t="str">
+        <f>A57&amp;D57</f>
+        <v>4NA-10</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H57" s="1">
+        <v>1</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="58" customHeight="1" spans="1:14">
-      <c r="B58" s="4"/>
+      <c r="A58" s="1">
+        <v>5</v>
+      </c>
+      <c r="B58" s="4" t="str">
+        <f>A58&amp;D58</f>
+        <v>5NA-11</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H58" s="1">
+        <v>1</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="59" customHeight="1" spans="1:14">
-      <c r="B59" s="4"/>
+      <c r="A59" s="1">
+        <v>6</v>
+      </c>
+      <c r="B59" s="4" t="str">
+        <f>A59&amp;D59</f>
+        <v>6NA-12</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H59" s="1">
+        <v>1</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="60" customHeight="1" spans="1:14">
+      <c r="A60" s="1">
+        <v>7</v>
+      </c>
       <c r="B60" s="4"/>
+      <c r="C60" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="61" customHeight="1" spans="1:14">
       <c r="B61" s="4"/>
